--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2545,6 +2545,44 @@
       </c>
       <c r="F56" t="n">
         <v>2498.6357421875</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2522.320068359375</v>
+      </c>
+      <c r="H56" t="n">
+        <v>23.684326171875</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.9389897209706736</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.8493968255772361</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-13 04:31:11</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>24</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2515.279052734375</v>
       </c>
     </row>
   </sheetData>
@@ -2558,7 +2596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5949,6 +5987,24 @@
           <t>2514.172607,2511.222656,2510.258301,2512.547852,2511.814941,2511.960449,2510.958740,2509.290771,2509.900391,2508.754883,2507.893555,2509.531006,2506.952393,2503.866211,2503.761230,2501.847412,2500.639160,2498.188965,2499.522461,2496.629150,2498.615723,2497.742920,2497.243652,2498.635742</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2511.459961,2519.050049,2523.629883,2533.050049,2530.540039,2533.090088,2536.090088,2535.219971,2543.969971,2539.100098,2534.510010,2531.340088,2525.350098,2522.010010,2518.919922,2520.040039,2523.360107,2522.639893,2525.350098,2524.419922,2525.239990,2521.090088,2520.159912,2522.320068</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2.712646,7.827393,13.371582,20.502197,18.725098,21.129639,25.131348,25.929200,34.069580,30.345215,26.616455,21.809082,18.397705,18.143799,15.158692,18.192627,22.720947,24.450928,25.827637,27.790772,26.624267,23.347168,22.916260,23.684326</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>0.108011,0.310728,0.529855,0.809388,0.739965,0.834145,0.990949,1.022759,1.339229,1.195117,1.050162,0.861563,0.728521,0.719418,0.601793,0.721918,0.900424,0.969260,1.022735,1.100878,1.054326,0.926074,0.909318,0.938990</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>0.8493968255772361</v>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>2507.114014,2508.676270,2509.011719,2510.290527,2510.705811,2507.895508,2503.546631,2508.258789,2502.683350,2508.920166,2502.797852,2502.180664,2495.768799,2498.662842,2495.635498,2496.572021,2490.516113,2486.149414,2488.199707,2484.714600,2488.267822,2489.264404,2488.290283,2486.154297</t>
@@ -5962,6 +6018,49 @@
       <c r="M56" t="inlineStr">
         <is>
           <t>2508.440918,2502.010254,2501.103027,2503.218750,2500.975586,2496.647217,2492.698486,2489.862793,2491.879395,2489.066650,2485.404053,2485.540771,2483.687988,2479.250244,2479.024902,2477.735840,2473.328857,2469.929932,2469.592285,2469.004883,2470.828369,2464.856201,2463.799072,2466.952637</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-13 04:31:11</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>24</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2524.219238,2523.064453,2522.627197,2525.288330,2522.867920,2522.976318,2522.360107,2521.075439,2522.035889,2522.583008,2520.303467,2520.196777,2520.034912,2517.434570,2518.314453,2517.497803,2517.796875,2515.723877,2516.052002,2517.721191,2516.963867,2516.829590,2516.589111,2515.279053</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2519.390625,2519.127441,2522.306396,2522.783203,2525.635010,2517.840820,2517.898193,2519.263672,2513.365723,2516.724365,2514.617676,2511.107178,2510.825928,2515.171143,2506.054688,2507.293213,2506.454346,2504.436279,2505.993408,2504.721924,2502.367188,2502.098633,2505.757324,2503.041992</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2509.492188,2508.722900,2502.729248,2506.118164,2498.579102,2496.341309,2492.684082,2487.437744,2483.643066,2481.217285,2472.731201,2472.309570,2468.394531,2467.840088,2463.730713,2462.025146,2460.913818,2459.290283,2451.122803,2450.628174,2449.274414,2449.349609,2447.405273,2443.746582</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2519.439941,2514.721924,2512.451416,2514.999756,2510.518066,2508.009277,2504.799316,2502.281006,2504.239502,2502.507812,2496.376221,2495.180176,2495.010986,2490.975830,2490.677246,2490.508057,2489.897705,2488.684082,2486.475586,2489.018066,2487.427246,2484.517578,2484.045410,2485.802734</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2583,6 +2583,44 @@
       </c>
       <c r="F57" t="n">
         <v>2515.279052734375</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2512.820068359375</v>
+      </c>
+      <c r="H57" t="n">
+        <v>2.458984375</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.09785755876287136</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.9312219916479936</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-14 04:37:31</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>24</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2501.372802734375</v>
       </c>
     </row>
   </sheetData>
@@ -2596,7 +2634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6048,6 +6086,24 @@
           <t>2524.219238,2523.064453,2522.627197,2525.288330,2522.867920,2522.976318,2522.360107,2521.075439,2522.035889,2522.583008,2520.303467,2520.196777,2520.034912,2517.434570,2518.314453,2517.497803,2517.796875,2515.723877,2516.052002,2517.721191,2516.963867,2516.829590,2516.589111,2515.279053</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2522.020020,2512.370117,2517.020020,2493.330078,2484.270020,2471.030029,2480.790039,2476.590088,2478.370117,2491.929932,2490.199951,2504.000000,2504.100098,2508.500000,2505.219971,2511.939941,2507.820068,2474.570068,2475.879883,2483.129883,2492.199951,2510.310059,2511.760010,2512.820068</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2.199218,10.694336,5.607177,31.958252,38.597900,51.946289,41.570068,44.485351,43.665772,30.653076,30.103516,16.196777,15.934814,8.934570,13.094482,5.557862,9.976807,41.153809,40.172119,34.591308,24.763916,6.519531,4.829101,2.458985</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>0.087201,0.425667,0.222770,1.281750,1.553692,2.102212,1.675679,1.796234,1.761875,1.230094,1.208879,0.646836,0.636349,0.356172,0.522688,0.221258,0.397828,1.663069,1.622539,1.393053,0.993657,0.259710,0.192260,0.097858</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>0.9312219916479936</v>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>2519.390625,2519.127441,2522.306396,2522.783203,2525.635010,2517.840820,2517.898193,2519.263672,2513.365723,2516.724365,2514.617676,2511.107178,2510.825928,2515.171143,2506.054688,2507.293213,2506.454346,2504.436279,2505.993408,2504.721924,2502.367188,2502.098633,2505.757324,2503.041992</t>
@@ -6061,6 +6117,49 @@
       <c r="M57" t="inlineStr">
         <is>
           <t>2519.439941,2514.721924,2512.451416,2514.999756,2510.518066,2508.009277,2504.799316,2502.281006,2504.239502,2502.507812,2496.376221,2495.180176,2495.010986,2490.975830,2490.677246,2490.508057,2489.897705,2488.684082,2486.475586,2489.018066,2487.427246,2484.517578,2484.045410,2485.802734</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-14 04:37:31</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>24</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2511.529297,2511.153564,2509.254395,2510.665771,2508.054932,2507.601807,2507.203613,2505.926758,2506.190674,2506.169922,2505.758789,2506.990234,2507.315430,2506.136963,2506.448486,2506.600830,2505.091064,2504.133789,2503.577881,2504.594238,2503.554688,2502.595703,2501.832031,2501.372803</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2506.816162,2507.473145,2507.875488,2508.250977,2509.585205,2504.241455,2504.584473,2505.142578,2501.926270,2503.766846,2501.758301,2498.230957,2499.023926,2504.990723,2500.337402,2498.363770,2499.585693,2497.510986,2497.273682,2494.685547,2497.315186,2491.571533,2494.017822,2494.363281</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2495.761963,2494.998535,2487.178223,2490.467285,2483.950195,2483.906738,2480.343750,2475.326416,2472.899658,2470.688232,2466.388672,2466.492188,2462.763428,2464.709473,2462.848877,2462.183350,2460.603760,2461.050781,2451.563721,2451.603516,2450.928223,2451.345947,2448.876465,2446.156494</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2504.379883,2501.125000,2496.260010,2498.209473,2493.600098,2491.447510,2489.401123,2487.833740,2488.275635,2486.978516,2481.719971,2483.723389,2484.440186,2481.839111,2482.413086,2484.007324,2480.343750,2480.745605,2477.296875,2479.455078,2477.642578,2474.838623,2474.218018,2475.631104</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2621,6 +2621,44 @@
       </c>
       <c r="F58" t="n">
         <v>2501.372802734375</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2489.72998046875</v>
+      </c>
+      <c r="H58" t="n">
+        <v>11.642822265625</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.467633934481239</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.6059458674686887</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-15 04:37:59</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>24</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2495.127197265625</v>
       </c>
     </row>
   </sheetData>
@@ -2634,7 +2672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6147,6 +6185,24 @@
           <t>2511.529297,2511.153564,2509.254395,2510.665771,2508.054932,2507.601807,2507.203613,2505.926758,2506.190674,2506.169922,2505.758789,2506.990234,2507.315430,2506.136963,2506.448486,2506.600830,2505.091064,2504.133789,2503.577881,2504.594238,2503.554688,2502.595703,2501.832031,2501.372803</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2515.489990,2513.370117,2521.750000,2517.500000,2522.909912,2512.000000,2508.060059,2504.189941,2499.169922,2500.600098,2507.570068,2528.620117,2533.429932,2539.050049,2539.520020,2570.449951,2546.530029,2532.870117,2515.780029,2515.649902,2515.030029,2511.709961,2498.209961,2489.729980</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>3.960693,2.216553,12.495605,6.834229,14.854980,4.398193,0.856446,1.736817,7.020752,5.569824,1.811279,21.629883,26.114502,32.913086,33.071534,63.849121,41.438965,28.736328,12.202148,11.055664,11.475341,9.114258,3.622070,11.642823</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>0.157452,0.088190,0.495513,0.271469,0.588803,0.175087,0.034148,0.069356,0.280923,0.222740,0.072232,0.855403,1.030796,1.296276,1.302275,2.483967,1.627272,1.134536,0.485024,0.439475,0.456271,0.362871,0.144987,0.467634</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>0.6059458674686887</v>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>2506.816162,2507.473145,2507.875488,2508.250977,2509.585205,2504.241455,2504.584473,2505.142578,2501.926270,2503.766846,2501.758301,2498.230957,2499.023926,2504.990723,2500.337402,2498.363770,2499.585693,2497.510986,2497.273682,2494.685547,2497.315186,2491.571533,2494.017822,2494.363281</t>
@@ -6160,6 +6216,49 @@
       <c r="M58" t="inlineStr">
         <is>
           <t>2504.379883,2501.125000,2496.260010,2498.209473,2493.600098,2491.447510,2489.401123,2487.833740,2488.275635,2486.978516,2481.719971,2483.723389,2484.440186,2481.839111,2482.413086,2484.007324,2480.343750,2480.745605,2477.296875,2479.455078,2477.642578,2474.838623,2474.218018,2475.631104</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-15 04:37:59</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>24</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2494.013184,2493.719482,2493.864502,2496.667480,2495.725342,2496.713135,2496.669189,2496.963867,2496.915283,2496.708740,2496.285400,2497.055176,2497.557373,2496.513672,2498.220215,2499.088867,2498.201172,2496.403809,2498.000000,2497.752197,2497.211426,2495.477539,2495.468750,2495.127197</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2489.892578,2491.907715,2493.634277,2496.021973,2497.574951,2494.366699,2493.718994,2494.940918,2491.907715,2494.908691,2492.646484,2490.996826,2488.128174,2494.795166,2492.934082,2493.027588,2492.192139,2490.256836,2491.413818,2487.370605,2487.311279,2484.500244,2485.455811,2485.818115</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2479.313721,2478.907959,2474.699219,2479.228516,2473.388184,2474.251709,2471.436768,2468.967529,2464.083008,2462.310059,2459.026123,2460.258057,2456.295166,2457.873535,2456.107178,2455.637939,2454.822266,2453.152344,2447.814697,2445.829346,2444.802490,2443.747070,2442.908203,2439.630371</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2488.181152,2484.094727,2482.322754,2485.093262,2482.531250,2481.931885,2480.661133,2479.610352,2480.961426,2478.052979,2474.897461,2476.082520,2477.205566,2475.364990,2477.032471,2478.842041,2475.806641,2475.280273,2474.524170,2475.436035,2474.099121,2468.800537,2469.576660,2470.105957</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2659,6 +2659,44 @@
       </c>
       <c r="F59" t="n">
         <v>2495.127197265625</v>
+      </c>
+      <c r="G59" t="n">
+        <v>2401.389892578125</v>
+      </c>
+      <c r="H59" t="n">
+        <v>93.7373046875</v>
+      </c>
+      <c r="I59" t="n">
+        <v>3.903460449184447</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2.671122287533258</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-16 04:33:14</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>24</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2416.831787109375</v>
       </c>
     </row>
   </sheetData>
@@ -2672,7 +2710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6246,6 +6284,24 @@
           <t>2494.013184,2493.719482,2493.864502,2496.667480,2495.725342,2496.713135,2496.669189,2496.963867,2496.915283,2496.708740,2496.285400,2497.055176,2497.557373,2496.513672,2498.220215,2499.088867,2498.201172,2496.403809,2498.000000,2497.752197,2497.211426,2495.477539,2495.468750,2495.127197</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2495.969971,2485.520020,2473.090088,2476.229980,2473.429932,2482.669922,2475.350098,2478.709961,2452.320068,2405.409912,2423.199951,2420.879883,2439.610107,2401.260010,2414.330078,2405.860107,2390.169922,2395.159912,2396.139893,2397.739990,2389.090088,2401.159912,2400.090088,2401.389893</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>1.956787,8.199462,20.774414,20.437500,22.295410,14.043213,21.319091,18.253906,44.595215,91.298828,73.085449,76.175293,57.947266,95.253662,83.890137,93.228760,108.031250,101.243897,101.860107,100.012207,108.121338,94.317627,95.378662,93.737304</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>0.078398,0.329889,0.840018,0.825347,0.901396,0.565650,0.861256,0.736428,1.818491,3.795562,3.016072,3.146595,2.375267,3.966820,3.474676,3.875070,4.519815,4.227020,4.251008,4.171103,4.525628,3.928003,3.973962,3.903460</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>2.671122287533258</v>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>2489.892578,2491.907715,2493.634277,2496.021973,2497.574951,2494.366699,2493.718994,2494.940918,2491.907715,2494.908691,2492.646484,2490.996826,2488.128174,2494.795166,2492.934082,2493.027588,2492.192139,2490.256836,2491.413818,2487.370605,2487.311279,2484.500244,2485.455811,2485.818115</t>
@@ -6259,6 +6315,49 @@
       <c r="M59" t="inlineStr">
         <is>
           <t>2488.181152,2484.094727,2482.322754,2485.093262,2482.531250,2481.931885,2480.661133,2479.610352,2480.961426,2478.052979,2474.897461,2476.082520,2477.205566,2475.364990,2477.032471,2478.842041,2475.806641,2475.280273,2474.524170,2475.436035,2474.099121,2468.800537,2469.576660,2470.105957</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-16 04:33:14</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>24</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2401.581787,2401.795166,2401.674072,2403.460938,2403.313232,2404.891113,2405.854736,2405.004395,2404.819580,2405.659424,2403.711670,2408.094482,2409.380615,2408.746826,2411.403809,2412.521484,2413.061279,2412.305908,2414.625000,2416.960205,2416.435059,2416.996094,2415.714355,2416.831787</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2401.456787,2404.411621,2399.435059,2404.198730,2408.238525,2407.483887,2407.792480,2403.554443,2408.752686,2410.657227,2404.974854,2407.670898,2408.783447,2409.165771,2410.798828,2404.958008,2411.304199,2415.612793,2415.102051,2410.452881,2415.490967,2407.939209,2410.291992,2410.646484</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2383.177246,2382.755371,2374.977051,2376.109375,2370.416504,2368.589355,2370.020020,2365.461914,2357.478271,2354.925537,2349.099121,2355.821533,2350.462402,2350.110596,2349.427490,2345.080566,2345.215820,2340.629883,2337.574463,2337.118652,2334.609131,2334.254883,2331.061279,2328.836914</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2394.148438,2389.195801,2385.706787,2384.509521,2382.324219,2381.624756,2380.534912,2377.018066,2379.327393,2375.989746,2370.821533,2374.865234,2374.549561,2373.041748,2377.684814,2375.182861,2372.781494,2369.906006,2370.885254,2374.478027,2372.282959,2367.806152,2367.901611,2370.093262</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2697,6 +2697,44 @@
       </c>
       <c r="F60" t="n">
         <v>2416.831787109375</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2429.1298828125</v>
+      </c>
+      <c r="H60" t="n">
+        <v>12.298095703125</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.5062757570165822</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.3842546369393678</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-17 04:38:38</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>24</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2427.06201171875</v>
       </c>
     </row>
   </sheetData>
@@ -2710,7 +2748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6345,6 +6383,24 @@
           <t>2401.581787,2401.795166,2401.674072,2403.460938,2403.313232,2404.891113,2405.854736,2405.004395,2404.819580,2405.659424,2403.711670,2408.094482,2409.380615,2408.746826,2411.403809,2412.521484,2413.061279,2412.305908,2414.625000,2416.960205,2416.435059,2416.996094,2415.714355,2416.831787</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2405.330078,2404.729980,2394.760010,2400.770020,2403.899902,2403.000000,2420.760010,2404.760010,2392.169922,2387.540039,2391.290039,2389.989990,2387.199951,2395.540039,2407.389893,2408.580078,2402.860107,2390.699951,2416.449951,2416.600098,2425.560059,2426.959961,2433.409912,2429.129883</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>3.748291,2.934814,6.914062,2.690918,0.586670,1.891113,14.905274,0.244385,12.649658,18.119385,12.421631,18.104492,22.180664,13.206787,4.013916,3.941406,10.201172,21.605957,1.824951,0.360107,9.125000,9.963867,17.695557,12.298096</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>0.155833,0.122043,0.288716,0.112086,0.024405,0.078698,0.615727,0.010163,0.528794,0.758914,0.519453,0.757513,0.929150,0.551307,0.166733,0.163640,0.424543,0.903750,0.075522,0.014901,0.376202,0.410549,0.727192,0.506276</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>0.3842546369393678</v>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>2401.456787,2404.411621,2399.435059,2404.198730,2408.238525,2407.483887,2407.792480,2403.554443,2408.752686,2410.657227,2404.974854,2407.670898,2408.783447,2409.165771,2410.798828,2404.958008,2411.304199,2415.612793,2415.102051,2410.452881,2415.490967,2407.939209,2410.291992,2410.646484</t>
@@ -6358,6 +6414,49 @@
       <c r="M60" t="inlineStr">
         <is>
           <t>2394.148438,2389.195801,2385.706787,2384.509521,2382.324219,2381.624756,2380.534912,2377.018066,2379.327393,2375.989746,2370.821533,2374.865234,2374.549561,2373.041748,2377.684814,2375.182861,2372.781494,2369.906006,2370.885254,2374.478027,2372.282959,2367.806152,2367.901611,2370.093262</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-17 04:38:38</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>24</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2428.214355,2428.813232,2429.229736,2429.704834,2430.495850,2430.519287,2431.032227,2430.819580,2429.231934,2429.314941,2428.743408,2429.966553,2430.403564,2428.615723,2429.325195,2428.508301,2427.170898,2428.138916,2428.213135,2428.328125,2428.364014,2428.088623,2427.228027,2427.062012</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2425.170654,2428.025879,2428.457764,2430.021240,2433.554443,2428.477539,2429.636230,2427.808350,2428.246582,2430.783203,2428.670898,2425.476074,2428.110596,2426.705322,2428.098145,2422.740723,2425.894775,2426.593018,2429.205078,2423.703125,2426.056152,2423.128418,2419.877930,2420.264160</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2415.996826,2415.165527,2409.948486,2409.249023,2405.391357,2402.978760,2403.089844,2399.914307,2392.333496,2388.783691,2385.120117,2385.942871,2381.558350,2380.621826,2379.208740,2373.095459,2370.506348,2368.999268,2362.248779,2358.988770,2359.254150,2358.231934,2356.726318,2352.141357</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2424.189697,2420.364746,2418.048828,2415.954590,2414.549072,2412.505371,2411.798828,2410.466553,2410.612305,2406.080078,2402.930664,2401.929443,2402.734619,2399.760986,2401.737549,2399.235107,2394.397461,2394.001953,2392.709473,2392.824219,2392.612061,2387.848389,2387.981201,2388.043945</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2735,6 +2735,44 @@
       </c>
       <c r="F61" t="n">
         <v>2427.06201171875</v>
+      </c>
+      <c r="G61" t="n">
+        <v>2470.909912109375</v>
+      </c>
+      <c r="H61" t="n">
+        <v>43.847900390625</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1.774564915367261</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.9143030519419714</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:23:54</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>24</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2467.618896484375</v>
       </c>
     </row>
   </sheetData>
@@ -2748,7 +2786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6444,6 +6482,24 @@
           <t>2428.214355,2428.813232,2429.229736,2429.704834,2430.495850,2430.519287,2431.032227,2430.819580,2429.231934,2429.314941,2428.743408,2429.966553,2430.403564,2428.615723,2429.325195,2428.508301,2427.170898,2428.138916,2428.213135,2428.328125,2428.364014,2428.088623,2427.228027,2427.062012</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2434.719971,2438.919922,2442.050049,2443.229980,2436.600098,2433.419922,2440.199951,2457.639893,2460.060059,2458.800049,2467.989990,2468.229980,2460.669922,2449.760010,2447.340088,2451.439941,2445.429932,2443.870117,2445.439941,2445.870117,2454.899902,2460.439941,2476.929932,2470.909912</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>6.505616,10.106690,12.820313,13.525146,6.104248,2.900635,9.167724,26.820313,30.828125,29.485108,39.246582,38.263427,30.266358,21.144287,18.014893,22.931640,18.259034,15.731201,17.226806,17.541992,26.535888,32.351318,49.701905,43.847900</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>0.267202,0.414392,0.524982,0.553576,0.250523,0.119200,0.375696,1.091304,1.253145,1.199167,1.590225,1.550238,1.230005,0.863117,0.736101,0.935436,0.746659,0.643700,0.704446,0.717209,1.080936,1.314859,2.006593,1.774565</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>0.9143030519419714</v>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>2425.170654,2428.025879,2428.457764,2430.021240,2433.554443,2428.477539,2429.636230,2427.808350,2428.246582,2430.783203,2428.670898,2425.476074,2428.110596,2426.705322,2428.098145,2422.740723,2425.894775,2426.593018,2429.205078,2423.703125,2426.056152,2423.128418,2419.877930,2420.264160</t>
@@ -6457,6 +6513,49 @@
       <c r="M61" t="inlineStr">
         <is>
           <t>2424.189697,2420.364746,2418.048828,2415.954590,2414.549072,2412.505371,2411.798828,2410.466553,2410.612305,2406.080078,2402.930664,2401.929443,2402.734619,2399.760986,2401.737549,2399.235107,2394.397461,2394.001953,2392.709473,2392.824219,2392.612061,2387.848389,2387.981201,2388.043945</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-18 04:23:54</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>24</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2468.671631,2469.295166,2469.177246,2470.853516,2469.581787,2469.175049,2469.432861,2469.316406,2469.039795,2468.866211,2468.907715,2469.439209,2469.634277,2467.895508,2468.610840,2469.725586,2469.526123,2468.030029,2468.454834,2468.617676,2467.934326,2467.620605,2468.207764,2467.618896</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2464.961670,2466.962402,2467.931152,2469.496338,2470.307861,2468.245117,2468.308594,2465.160645,2466.064941,2467.766846,2467.633545,2464.310547,2466.595947,2466.159912,2465.081299,2465.889160,2465.235352,2465.039062,2465.750244,2463.349609,2462.380371,2463.681396,2458.972412,2461.966309</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2453.729248,2452.896973,2448.275391,2449.240234,2444.370117,2441.825439,2441.596436,2439.501953,2434.586914,2432.428711,2430.109375,2430.716553,2427.289551,2426.917236,2426.302246,2423.229492,2423.094971,2420.411621,2413.595703,2412.034668,2411.476807,2412.654541,2412.056641,2407.451904</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2462.817383,2458.885742,2456.851807,2456.589844,2453.709961,2451.337646,2450.252441,2449.948486,2450.808838,2447.294189,2444.412354,2444.248535,2446.661133,2443.737305,2444.029297,2443.955078,2441.513672,2440.312500,2438.223877,2439.534668,2438.345459,2434.137451,2435.920410,2434.624023</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2773,6 +2773,44 @@
       </c>
       <c r="F62" t="n">
         <v>2467.618896484375</v>
+      </c>
+      <c r="G62" t="n">
+        <v>2621.52001953125</v>
+      </c>
+      <c r="H62" t="n">
+        <v>153.901123046875</v>
+      </c>
+      <c r="I62" t="n">
+        <v>5.870682729876457</v>
+      </c>
+      <c r="J62" t="n">
+        <v>3.976506701322608</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:20:47</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>24</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2604.612060546875</v>
       </c>
     </row>
   </sheetData>
@@ -2786,7 +2824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6543,6 +6581,24 @@
           <t>2468.671631,2469.295166,2469.177246,2470.853516,2469.581787,2469.175049,2469.432861,2469.316406,2469.039795,2468.866211,2468.907715,2469.439209,2469.634277,2467.895508,2468.610840,2469.725586,2469.526123,2468.030029,2468.454834,2468.617676,2467.934326,2467.620605,2468.207764,2467.618896</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2478.370117,2484.919922,2487.600098,2503.159912,2505.830078,2511.350098,2505.800049,2500.159912,2552.790039,2581.590088,2583.219971,2596.489990,2606.780029,2611.669922,2636.800049,2631.540039,2626.310059,2619.689941,2611.340088,2626.199951,2612.469971,2622.639893,2619.330078,2621.520020</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>9.698486,15.624756,18.422852,32.306396,36.248291,42.175049,36.367188,30.843506,83.750244,112.723877,114.312256,127.050781,137.145752,143.774414,168.189209,161.814453,156.783936,151.659912,142.885254,157.582275,144.535645,155.019288,151.122314,153.901124</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>0.391325,0.628783,0.740587,1.290625,1.446558,1.679378,1.451320,1.233661,3.280734,4.366451,4.425185,4.893174,5.261117,5.505076,6.378535,6.149040,5.969742,5.789231,5.471721,6.000391,5.532528,5.910811,5.769502,5.870683</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>3.976506701322608</v>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
           <t>2464.961670,2466.962402,2467.931152,2469.496338,2470.307861,2468.245117,2468.308594,2465.160645,2466.064941,2467.766846,2467.633545,2464.310547,2466.595947,2466.159912,2465.081299,2465.889160,2465.235352,2465.039062,2465.750244,2463.349609,2462.380371,2463.681396,2458.972412,2461.966309</t>
@@ -6556,6 +6612,49 @@
       <c r="M62" t="inlineStr">
         <is>
           <t>2462.817383,2458.885742,2456.851807,2456.589844,2453.709961,2451.337646,2450.252441,2449.948486,2450.808838,2447.294189,2444.412354,2444.248535,2446.661133,2443.737305,2444.029297,2443.955078,2441.513672,2440.312500,2438.223877,2439.534668,2438.345459,2434.137451,2435.920410,2434.624023</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-19 04:20:47</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>24</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2619.850098,2618.833984,2619.124756,2619.798096,2617.849121,2618.840332,2616.787842,2615.148682,2616.308838,2616.075684,2614.940918,2614.324463,2613.169189,2611.223633,2611.415039,2610.205078,2611.038818,2608.357666,2607.308594,2606.996826,2605.859131,2604.505371,2605.015381,2604.612061</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2616.611816,2611.046387,2621.132568,2619.485352,2616.653809,2614.125000,2608.034424,2612.656250,2606.433594,2610.486328,2610.608154,2604.982178,2601.900146,2606.846924,2600.628418,2606.344238,2604.686523,2595.297852,2595.536621,2602.320312,2593.602051,2597.891602,2592.776123,2591.293457</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2597.629395,2595.933838,2589.860596,2588.249268,2582.325439,2578.634277,2570.576172,2567.136963,2564.332275,2561.205811,2555.802734,2554.436035,2551.725342,2548.394287,2541.977539,2540.557373,2539.791992,2537.982178,2525.111816,2521.430908,2519.265381,2518.987305,2515.601562,2513.469727</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2609.902100,2606.436279,2603.187744,2603.370850,2598.357178,2594.860840,2591.136963,2587.505127,2589.984619,2588.347900,2583.670166,2581.687744,2582.337402,2577.733398,2573.337646,2574.867676,2572.791016,2572.318848,2565.364258,2564.342285,2561.693359,2555.048584,2554.955078,2556.727295</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2811,6 +2811,44 @@
       </c>
       <c r="F63" t="n">
         <v>2604.612060546875</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2584.989990234375</v>
+      </c>
+      <c r="H63" t="n">
+        <v>19.6220703125</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.7590772260870887</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.8130355790320722</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-20 04:39:51</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>24</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2573.0166015625</v>
       </c>
     </row>
   </sheetData>
@@ -2824,7 +2862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6642,6 +6680,24 @@
           <t>2619.850098,2618.833984,2619.124756,2619.798096,2617.849121,2618.840332,2616.787842,2615.148682,2616.308838,2616.075684,2614.940918,2614.324463,2613.169189,2611.223633,2611.415039,2610.205078,2611.038818,2608.357666,2607.308594,2606.996826,2605.859131,2604.505371,2605.015381,2604.612061</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2628.090088,2626.389893,2626.010010,2644.399902,2640.189941,2637.260010,2638.590088,2641.550049,2637.629883,2638.280029,2640.590088,2649.870117,2644.929932,2638.399902,2634.330078,2635.379883,2627.560059,2630.110107,2633.639893,2626.729980,2618.389893,2573.719971,2587.179932,2584.989990</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>8.239990,7.555909,6.885254,24.601806,22.340820,18.419678,21.802246,26.401367,21.321045,22.204345,25.649170,35.545654,31.760743,27.176269,22.915039,25.174805,16.521241,21.752441,26.331299,19.733154,12.530762,30.785400,17.835449,19.622071</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>0.313535,0.287692,0.262194,0.930336,0.846182,0.698440,0.826284,0.999465,0.808341,0.841622,0.971342,1.341411,1.200816,1.030028,0.869862,0.955263,0.628767,0.827054,0.999806,0.751244,0.478567,1.196144,0.689378,0.759077</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>0.8130355790320722</v>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
           <t>2616.611816,2611.046387,2621.132568,2619.485352,2616.653809,2614.125000,2608.034424,2612.656250,2606.433594,2610.486328,2610.608154,2604.982178,2601.900146,2606.846924,2600.628418,2606.344238,2604.686523,2595.297852,2595.536621,2602.320312,2593.602051,2597.891602,2592.776123,2591.293457</t>
@@ -6655,6 +6711,49 @@
       <c r="M63" t="inlineStr">
         <is>
           <t>2609.902100,2606.436279,2603.187744,2603.370850,2598.357178,2594.860840,2591.136963,2587.505127,2589.984619,2588.347900,2583.670166,2581.687744,2582.337402,2577.733398,2573.337646,2574.867676,2572.791016,2572.318848,2565.364258,2564.342285,2561.693359,2555.048584,2554.955078,2556.727295</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-20 04:39:51</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>24</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2584.962402,2582.970703,2583.013916,2584.280273,2582.760986,2583.122559,2583.004883,2580.478516,2581.409912,2581.029541,2579.954590,2579.697021,2580.133545,2578.172852,2578.564697,2577.758301,2578.804932,2577.727783,2576.597412,2577.950928,2575.677979,2575.666504,2575.269775,2573.016602</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2583.296875,2579.106201,2582.176758,2582.227539,2584.707520,2581.604248,2577.694580,2576.865967,2577.244141,2574.880127,2577.697998,2574.236084,2568.999023,2574.440186,2566.885498,2565.688232,2571.671143,2565.289551,2567.618652,2568.403320,2562.612793,2561.485107,2565.945312,2560.839600</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2566.563477,2564.101318,2557.594727,2556.798828,2550.627686,2547.403320,2543.250000,2536.821777,2532.911133,2529.845459,2523.492432,2521.917236,2519.267090,2515.915527,2511.027832,2507.796875,2505.193848,2503.628174,2491.203857,2490.511230,2484.823242,2485.523682,2481.483643,2477.404785</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2576.239258,2571.485352,2568.034668,2569.344482,2565.169189,2563.227051,2560.091064,2555.585205,2556.701172,2555.118896,2549.637451,2549.017334,2547.862305,2543.290527,2541.326660,2540.556396,2538.291748,2536.828125,2531.795898,2532.901367,2527.702148,2524.234131,2522.557129,2520.440186</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2849,6 +2849,44 @@
       </c>
       <c r="F64" t="n">
         <v>2573.0166015625</v>
+      </c>
+      <c r="G64" t="n">
+        <v>2659.2099609375</v>
+      </c>
+      <c r="H64" t="n">
+        <v>86.193359375</v>
+      </c>
+      <c r="I64" t="n">
+        <v>3.24131454985272</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1.55572395949543</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-21 04:37:45</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>24</v>
+      </c>
+      <c r="F65" t="n">
+        <v>2641.02001953125</v>
       </c>
     </row>
   </sheetData>
@@ -2862,7 +2900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6741,6 +6779,24 @@
           <t>2584.962402,2582.970703,2583.013916,2584.280273,2582.760986,2583.122559,2583.004883,2580.478516,2581.409912,2581.029541,2579.954590,2579.697021,2580.133545,2578.172852,2578.564697,2577.758301,2578.804932,2577.727783,2576.597412,2577.950928,2575.677979,2575.666504,2575.269775,2573.016602</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2577.159912,2573.260010,2576.040039,2573.879883,2578.800049,2570.489990,2577.870117,2579.399902,2580.010010,2584.879883,2612.479980,2640.300049,2626.260010,2625.620117,2632.969971,2634.219971,2630.179932,2638.949951,2644.090088,2689.179932,2649.590088,2661.139893,2665.219971,2659.209961</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>7.802490,9.710693,6.973877,10.400390,3.960937,12.632569,5.134766,1.078614,1.399902,3.850342,32.525390,60.603028,46.126465,47.447265,54.405274,56.461670,51.375000,61.222168,67.492676,111.229004,73.912109,85.473389,89.950196,86.193359</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>0.302755,0.377369,0.270721,0.404074,0.153596,0.491446,0.199186,0.041816,0.054260,0.148956,1.245001,2.295308,1.756356,1.807088,2.066308,2.143392,1.953288,2.319944,2.552586,4.136168,2.789568,3.211909,3.374963,3.241315</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>1.55572395949543</v>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>2583.296875,2579.106201,2582.176758,2582.227539,2584.707520,2581.604248,2577.694580,2576.865967,2577.244141,2574.880127,2577.697998,2574.236084,2568.999023,2574.440186,2566.885498,2565.688232,2571.671143,2565.289551,2567.618652,2568.403320,2562.612793,2561.485107,2565.945312,2560.839600</t>
@@ -6754,6 +6810,49 @@
       <c r="M64" t="inlineStr">
         <is>
           <t>2576.239258,2571.485352,2568.034668,2569.344482,2565.169189,2563.227051,2560.091064,2555.585205,2556.701172,2555.118896,2549.637451,2549.017334,2547.862305,2543.290527,2541.326660,2540.556396,2538.291748,2536.828125,2531.795898,2532.901367,2527.702148,2524.234131,2522.557129,2520.440186</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-21 04:37:45</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>24</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2656.028564,2655.041992,2652.694092,2653.339111,2652.802734,2653.840332,2651.909180,2649.870605,2650.971680,2649.109619,2648.107910,2648.375488,2648.032959,2645.606934,2645.769531,2646.751953,2647.479004,2644.446045,2644.358154,2644.836670,2645.147949,2642.814453,2642.306396,2641.020020</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>2652.256104,2650.644531,2652.804932,2654.034424,2653.290771,2650.645996,2643.546875,2650.641602,2644.779785,2646.126709,2644.004883,2641.772461,2639.849121,2641.956299,2637.274902,2637.700439,2641.443359,2635.177002,2638.054688,2635.493164,2634.937744,2637.465332,2636.066162,2631.143799</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2634.244873,2631.553955,2623.501709,2622.713867,2616.748535,2614.713623,2611.116211,2605.540771,2601.702881,2596.601562,2591.301270,2591.374512,2587.461670,2584.454102,2581.652344,2580.835693,2580.054688,2576.402832,2564.433105,2561.611084,2562.581543,2561.298584,2557.334229,2552.355469</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2645.228271,2640.717529,2636.041748,2635.415039,2632.064453,2629.587891,2627.667969,2623.396729,2624.119385,2620.666016,2616.524902,2615.582764,2617.202393,2611.442627,2609.492676,2611.510986,2609.671143,2606.257324,2600.580322,2602.311035,2599.721191,2593.396240,2591.854004,2592.287109</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2887,6 +2887,44 @@
       </c>
       <c r="F65" t="n">
         <v>2641.02001953125</v>
+      </c>
+      <c r="G65" t="n">
+        <v>2731.18994140625</v>
+      </c>
+      <c r="H65" t="n">
+        <v>90.169921875</v>
+      </c>
+      <c r="I65" t="n">
+        <v>3.301488501695814</v>
+      </c>
+      <c r="J65" t="n">
+        <v>3.148459440070025</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-22 04:33:43</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>24</v>
+      </c>
+      <c r="F66" t="n">
+        <v>2714.780517578125</v>
       </c>
     </row>
   </sheetData>
@@ -2900,7 +2938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6840,6 +6878,24 @@
           <t>2656.028564,2655.041992,2652.694092,2653.339111,2652.802734,2653.840332,2651.909180,2649.870605,2650.971680,2649.109619,2648.107910,2648.375488,2648.032959,2645.606934,2645.769531,2646.751953,2647.479004,2644.446045,2644.358154,2644.836670,2645.147949,2642.814453,2642.306396,2641.020020</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2664.639893,2662.790039,2660.639893,2696.020020,2720.040039,2715.219971,2724.530029,2734.860107,2730.750000,2736.389893,2755.239990,2754.590088,2743.429932,2758.139893,2762.050049,2784.560059,2768.159912,2778.600098,2775.580078,2754.389893,2748.219971,2739.280029,2738.810059,2731.189941</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>8.611329,7.748047,7.945801,42.680909,67.237305,61.379639,72.620849,84.989502,79.778320,87.280274,107.132080,106.214600,95.396973,112.532959,116.280518,137.808106,120.680908,134.154053,131.221924,109.553223,103.072022,96.465576,96.503663,90.169921</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>0.323170,0.290975,0.298642,1.583108,2.471923,2.260577,2.665445,3.107636,2.921480,3.189614,3.888303,3.855913,3.477288,4.080031,4.209935,4.949008,4.359608,4.828117,4.727730,3.977404,3.750501,3.521567,3.523562,3.301488</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>3.148459440070025</v>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
           <t>2652.256104,2650.644531,2652.804932,2654.034424,2653.290771,2650.645996,2643.546875,2650.641602,2644.779785,2646.126709,2644.004883,2641.772461,2639.849121,2641.956299,2637.274902,2637.700439,2641.443359,2635.177002,2638.054688,2635.493164,2634.937744,2637.465332,2636.066162,2631.143799</t>
@@ -6853,6 +6909,49 @@
       <c r="M65" t="inlineStr">
         <is>
           <t>2645.228271,2640.717529,2636.041748,2635.415039,2632.064453,2629.587891,2627.667969,2623.396729,2624.119385,2620.666016,2616.524902,2615.582764,2617.202393,2611.442627,2609.492676,2611.510986,2609.671143,2606.257324,2600.580322,2602.311035,2599.721191,2593.396240,2591.854004,2592.287109</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-22 04:33:43</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>24</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2729.935059,2727.600342,2726.299561,2727.388916,2725.538086,2725.895264,2725.618652,2723.394287,2725.446777,2724.914551,2722.700195,2723.068115,2719.690430,2717.708740,2719.286621,2720.023193,2721.932373,2719.895264,2720.659912,2717.448975,2719.990234,2715.892090,2715.534424,2714.780518</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>2724.336426,2723.224854,2721.318115,2725.277344,2723.834473,2721.169922,2714.707764,2723.644775,2715.282959,2723.756592,2717.764160,2714.161377,2707.843506,2709.359863,2708.621582,2713.900391,2713.021973,2710.103027,2708.904541,2707.026123,2708.906738,2709.859131,2704.048828,2697.857910</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2706.341309,2702.343994,2693.223633,2691.044434,2686.987061,2683.840332,2680.190186,2675.638428,2671.842285,2665.916748,2660.558838,2659.977051,2654.579590,2651.052979,2646.892090,2645.700684,2645.718262,2643.222168,2631.672119,2623.113281,2623.729004,2620.603027,2617.450439,2614.864746</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2718.079346,2712.499756,2707.000000,2706.851074,2702.476318,2699.761230,2699.215820,2693.012451,2696.504395,2691.894043,2686.672607,2685.336182,2683.283203,2677.953613,2676.207520,2678.555664,2676.830566,2673.424072,2669.377930,2665.406494,2664.333008,2655.154053,2655.189941,2656.312744</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2925,6 +2925,44 @@
       </c>
       <c r="F66" t="n">
         <v>2714.780517578125</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2779.580078125</v>
+      </c>
+      <c r="H66" t="n">
+        <v>64.799560546875</v>
+      </c>
+      <c r="I66" t="n">
+        <v>2.331271585116063</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1.025061979687503</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-23 04:30:07</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>24</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2784.521240234375</v>
       </c>
     </row>
   </sheetData>
@@ -2938,7 +2976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6939,6 +6977,24 @@
           <t>2729.935059,2727.600342,2726.299561,2727.388916,2725.538086,2725.895264,2725.618652,2723.394287,2725.446777,2724.914551,2722.700195,2723.068115,2719.690430,2717.708740,2719.286621,2720.023193,2721.932373,2719.895264,2720.659912,2717.448975,2719.990234,2715.892090,2715.534424,2714.780518</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2732.679932,2730.010010,2726.129883,2748.330078,2750.209961,2741.590088,2741.620117,2755.800049,2758.030029,2742.620117,2743.889893,2745.719971,2753.949951,2752.260010,2751.860107,2751.360107,2747.310059,2752.800049,2753.379883,2759.610107,2753.969971,2762.090088,2773.679932,2779.580078</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2.744873,2.409668,0.169678,20.941162,24.671875,15.694824,16.001465,32.405762,32.583252,17.705566,21.189698,22.651856,34.259521,34.551270,32.573486,31.336914,25.377686,32.904785,32.719971,42.161132,33.979737,46.197998,58.145508,64.799560</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>0.100446,0.088266,0.006224,0.761960,0.897091,0.572472,0.583650,1.175911,1.181396,0.645571,0.772250,0.824988,1.244014,1.255378,1.183690,1.138961,0.923728,1.195321,1.188357,1.527793,1.233846,1.672574,2.096331,2.331272</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>1.025061979687503</v>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
           <t>2724.336426,2723.224854,2721.318115,2725.277344,2723.834473,2721.169922,2714.707764,2723.644775,2715.282959,2723.756592,2717.764160,2714.161377,2707.843506,2709.359863,2708.621582,2713.900391,2713.021973,2710.103027,2708.904541,2707.026123,2708.906738,2709.859131,2704.048828,2697.857910</t>
@@ -6952,6 +7008,49 @@
       <c r="M66" t="inlineStr">
         <is>
           <t>2718.079346,2712.499756,2707.000000,2706.851074,2702.476318,2699.761230,2699.215820,2693.012451,2696.504395,2691.894043,2686.672607,2685.336182,2683.283203,2677.953613,2676.207520,2678.555664,2676.830566,2673.424072,2669.377930,2665.406494,2664.333008,2655.154053,2655.189941,2656.312744</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-09-23 04:30:07</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>24</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2779.884033,2781.602783,2782.515625,2785.252686,2783.234375,2785.843994,2786.331543,2784.145996,2786.890381,2784.918945,2784.516357,2785.529297,2783.812500,2783.349609,2785.072266,2785.673096,2788.302490,2784.792725,2787.368896,2785.606201,2787.752441,2785.833740,2785.908447,2784.521240</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2771.349854,2776.485352,2778.367432,2779.276123,2781.091553,2780.210938,2776.903809,2785.035400,2777.061035,2781.326660,2775.599854,2776.356445,2774.900146,2774.680176,2774.360596,2777.598877,2778.350830,2771.940918,2777.015381,2775.949951,2775.999512,2780.750732,2769.129883,2772.006348</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2758.750000,2759.299316,2753.024902,2754.614014,2752.742432,2750.741455,2748.453125,2743.772217,2743.425049,2737.275879,2733.332031,2733.983643,2729.340332,2725.211914,2721.384766,2720.011963,2720.369873,2718.536377,2710.640137,2701.685791,2702.253906,2698.868164,2694.847412,2692.492676</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2768.483887,2768.569092,2767.265137,2769.126953,2765.161865,2764.632568,2765.942871,2761.090088,2764.195312,2758.468262,2756.044678,2756.221680,2757.629150,2749.303955,2748.347656,2751.195312,2750.968018,2747.294189,2745.093506,2740.850098,2738.986816,2733.481934,2731.793457,2731.870117</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2963,6 +2963,44 @@
       </c>
       <c r="F67" t="n">
         <v>2784.521240234375</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2674.389892578125</v>
+      </c>
+      <c r="H67" t="n">
+        <v>110.13134765625</v>
+      </c>
+      <c r="I67" t="n">
+        <v>4.117998948540852</v>
+      </c>
+      <c r="J67" t="n">
+        <v>3.252303250522301</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:27:20</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>24</v>
+      </c>
+      <c r="F68" t="n">
+        <v>2669.64501953125</v>
       </c>
     </row>
   </sheetData>
@@ -2976,7 +3014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7038,6 +7076,24 @@
           <t>2779.884033,2781.602783,2782.515625,2785.252686,2783.234375,2785.843994,2786.331543,2784.145996,2786.890381,2784.918945,2784.516357,2785.529297,2783.812500,2783.349609,2785.072266,2785.673096,2788.302490,2784.792725,2787.368896,2785.606201,2787.752441,2785.833740,2785.908447,2784.521240</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2757.399902,2754.040039,2742.580078,2734.639893,2733.149902,2737.399902,2727.419922,2721.189941,2715.189941,2675.949951,2656.100098,2660.290039,2667.600098,2668.469971,2678.100098,2671.120117,2677.129883,2689.530029,2682.530029,2682.280029,2674.580078,2685.090088,2676.179932,2674.389893</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>22.484131,27.562744,39.935547,50.612793,50.084473,48.444092,58.911621,62.956055,71.700440,108.968994,128.416259,125.239258,116.212402,114.879638,106.972168,114.552979,111.172607,95.262696,104.838867,103.326172,113.172363,100.743652,109.728515,110.131347</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>0.815411,1.000811,1.456131,1.850803,1.832482,1.769712,2.159976,2.313549,2.640715,4.072161,4.834767,4.707729,4.356440,4.305075,3.994330,4.288575,4.152679,3.541983,3.908209,3.852177,4.231407,3.751965,4.100192,4.117999</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>3.252303250522301</v>
+      </c>
       <c r="K67" t="inlineStr">
         <is>
           <t>2771.349854,2776.485352,2778.367432,2779.276123,2781.091553,2780.210938,2776.903809,2785.035400,2777.061035,2781.326660,2775.599854,2776.356445,2774.900146,2774.680176,2774.360596,2777.598877,2778.350830,2771.940918,2777.015381,2775.949951,2775.999512,2780.750732,2769.129883,2772.006348</t>
@@ -7051,6 +7107,49 @@
       <c r="M67" t="inlineStr">
         <is>
           <t>2768.483887,2768.569092,2767.265137,2769.126953,2765.161865,2764.632568,2765.942871,2761.090088,2764.195312,2758.468262,2756.044678,2756.221680,2757.629150,2749.303955,2748.347656,2751.195312,2750.968018,2747.294189,2745.093506,2740.850098,2738.986816,2733.481934,2731.793457,2731.870117</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-09-24 04:27:20</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>24</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2672.718506,2672.334473,2672.891113,2672.791504,2671.019531,2671.479492,2672.559814,2671.162354,2672.106934,2670.488770,2671.403809,2672.612061,2672.281738,2671.458252,2672.680664,2671.157227,2672.793945,2671.102295,2671.772461,2670.542480,2670.558594,2670.522705,2669.524414,2669.645020</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>2665.580566,2670.209717,2671.595215,2670.954590,2670.699219,2670.368652,2668.411621,2669.476562,2669.178711,2670.693604,2667.069580,2666.764648,2665.467041,2666.999023,2669.026855,2661.925781,2667.232422,2666.679688,2667.041016,2661.867920,2664.697266,2662.885742,2661.817627,2663.205811</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2652.559326,2649.296387,2644.702393,2641.758789,2637.673096,2634.247314,2632.514648,2628.452637,2625.953125,2621.799072,2617.554932,2618.082764,2615.692383,2612.910400,2609.467529,2606.306152,2604.595459,2603.493408,2593.752197,2588.919922,2588.354004,2587.687988,2583.333008,2581.163086</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2662.547852,2658.351562,2656.339355,2655.103027,2650.248535,2647.604492,2647.864746,2645.870361,2646.450195,2642.510010,2638.937256,2640.652588,2641.486328,2636.314697,2636.348145,2635.362793,2633.595947,2630.734619,2627.829102,2626.166748,2623.777344,2619.466553,2617.446289,2617.240723</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3001,6 +3001,44 @@
       </c>
       <c r="F68" t="n">
         <v>2669.64501953125</v>
+      </c>
+      <c r="G68" t="n">
+        <v>2680.60009765625</v>
+      </c>
+      <c r="H68" t="n">
+        <v>10.955078125</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.4086800614003722</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.5566469489590244</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:38:37</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>24</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2674.099609375</v>
       </c>
     </row>
   </sheetData>
@@ -3014,7 +3052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7137,6 +7175,24 @@
           <t>2672.718506,2672.334473,2672.891113,2672.791504,2671.019531,2671.479492,2672.559814,2671.162354,2672.106934,2670.488770,2671.403809,2672.612061,2672.281738,2671.458252,2672.680664,2671.157227,2672.793945,2671.102295,2671.772461,2670.542480,2670.558594,2670.522705,2669.524414,2669.645020</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2681.860107,2685.610107,2692.979980,2668.360107,2641.310059,2647.639893,2646.669922,2647.939941,2669.540039,2657.030029,2682.620117,2686.639893,2668.860107,2689.290039,2696.120117,2687.439941,2686.090088,2684.689941,2687.350098,2689.729980,2689.129883,2675.959961,2678.250000,2680.600098</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>9.141601,13.275634,20.088867,4.431397,29.709472,23.839599,25.889892,23.222413,2.566895,13.458741,11.216308,14.027832,3.421631,17.831787,23.439453,16.282714,13.296143,13.587646,15.577637,19.187500,18.571289,5.437256,8.725586,10.955078</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>0.340868,0.494325,0.745972,0.166072,1.124801,0.900409,0.978206,0.876999,0.096155,0.506533,0.418110,0.522133,0.128206,0.663067,0.869377,0.605882,0.495000,0.506116,0.579665,0.713362,0.690606,0.203189,0.325794,0.408680</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>0.5566469489590244</v>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
           <t>2665.580566,2670.209717,2671.595215,2670.954590,2670.699219,2670.368652,2668.411621,2669.476562,2669.178711,2670.693604,2667.069580,2666.764648,2665.467041,2666.999023,2669.026855,2661.925781,2667.232422,2666.679688,2667.041016,2661.867920,2664.697266,2662.885742,2661.817627,2663.205811</t>
@@ -7150,6 +7206,49 @@
       <c r="M68" t="inlineStr">
         <is>
           <t>2662.547852,2658.351562,2656.339355,2655.103027,2650.248535,2647.604492,2647.864746,2645.870361,2646.450195,2642.510010,2638.937256,2640.652588,2641.486328,2636.314697,2636.348145,2635.362793,2633.595947,2630.734619,2627.829102,2626.166748,2623.777344,2619.466553,2617.446289,2617.240723</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-09-25 04:38:37</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>24</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2677.689209,2678.006348,2678.183838,2679.217529,2677.013916,2677.095215,2676.931152,2676.222900,2676.891357,2676.367676,2675.588867,2678.000732,2678.884521,2678.789062,2678.814453,2678.442871,2678.582031,2677.674316,2677.608398,2676.366455,2675.578613,2675.812500,2674.282227,2674.099609</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2671.125977,2675.085693,2677.200928,2673.403320,2677.470703,2675.570068,2671.724854,2672.288330,2675.290039,2674.470947,2671.961426,2670.325684,2672.903076,2672.198975,2674.169434,2668.591064,2669.219482,2673.526367,2671.897705,2664.555664,2666.541260,2667.888428,2665.133789,2665.059814</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2657.677490,2656.051514,2650.730713,2650.421387,2646.657959,2643.757324,2640.402832,2637.780762,2635.157715,2631.633057,2626.894287,2628.041992,2625.815430,2623.813965,2619.985840,2618.198242,2614.247070,2613.457764,2604.379639,2600.359619,2598.163818,2598.114258,2594.019775,2590.850098</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2667.681641,2664.747314,2663.352783,2663.492188,2659.247070,2655.942627,2654.843994,2653.561768,2654.452393,2651.167236,2646.158691,2649.020264,2650.731934,2645.575684,2645.420410,2645.091064,2641.541260,2639.213135,2636.252930,2634.490479,2631.769287,2629.379150,2626.863037,2626.178711</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3039,6 +3039,44 @@
       </c>
       <c r="F69" t="n">
         <v>2674.099609375</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2687.739990234375</v>
+      </c>
+      <c r="H69" t="n">
+        <v>13.640380859375</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.5075037358128358</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.5531459546502335</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-26 04:42:28</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>24</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2680.1044921875</v>
       </c>
     </row>
   </sheetData>
@@ -3052,7 +3090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7236,6 +7274,24 @@
           <t>2677.689209,2678.006348,2678.183838,2679.217529,2677.013916,2677.095215,2676.931152,2676.222900,2676.891357,2676.367676,2675.588867,2678.000732,2678.884521,2678.789062,2678.814453,2678.442871,2678.582031,2677.674316,2677.608398,2676.366455,2675.578613,2675.812500,2674.282227,2674.099609</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2679.709961,2674.239990,2672.229980,2690.590088,2704.000000,2713.770020,2717.040039,2716.770020,2694.489990,2695.429932,2686.060059,2682.909912,2685.370117,2692.979980,2692.949951,2683.840088,2681.149902,2691.310059,2691.310059,2686.770020,2692.310059,2690.699951,2687.370117,2687.739990</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2.020752,3.766358,5.953858,11.372559,26.986084,36.674805,40.108887,40.547120,17.598633,19.062256,10.471192,4.909180,6.485596,14.190918,14.135498,5.397217,2.567871,13.635743,13.701661,10.403565,16.731446,14.887451,13.087890,13.640381</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>0.075409,0.140838,0.222805,0.422679,0.998006,1.351434,1.476198,1.492475,0.653134,0.707206,0.389835,0.182980,0.241516,0.526960,0.524908,0.201101,0.095775,0.506658,0.509107,0.387215,0.621453,0.553293,0.487015,0.507504</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>0.5531459546502335</v>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
           <t>2671.125977,2675.085693,2677.200928,2673.403320,2677.470703,2675.570068,2671.724854,2672.288330,2675.290039,2674.470947,2671.961426,2670.325684,2672.903076,2672.198975,2674.169434,2668.591064,2669.219482,2673.526367,2671.897705,2664.555664,2666.541260,2667.888428,2665.133789,2665.059814</t>
@@ -7249,6 +7305,49 @@
       <c r="M69" t="inlineStr">
         <is>
           <t>2667.681641,2664.747314,2663.352783,2663.492188,2659.247070,2655.942627,2654.843994,2653.561768,2654.452393,2651.167236,2646.158691,2649.020264,2650.731934,2645.575684,2645.420410,2645.091064,2641.541260,2639.213135,2636.252930,2634.490479,2631.769287,2629.379150,2626.863037,2626.178711</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-09-26 04:42:28</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>24</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2687.664062,2687.115723,2687.213135,2687.528320,2686.972168,2687.493408,2687.262939,2686.010986,2687.160889,2686.129639,2685.257080,2685.689453,2685.852051,2684.605957,2686.045410,2685.295654,2686.177734,2685.480469,2685.264893,2684.194824,2685.151123,2682.912109,2682.598633,2680.104492</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2682.612305,2685.500977,2687.326172,2681.082275,2688.514893,2685.236084,2684.377441,2681.090332,2684.940674,2682.128174,2682.203857,2678.068115,2680.087158,2680.740234,2680.901367,2678.145752,2680.697754,2680.491699,2679.937012,2673.132568,2675.779541,2676.539551,2677.989502,2673.056396</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2670.955811,2668.817139,2664.526611,2664.231445,2661.611328,2659.183105,2657.409424,2654.205078,2652.952393,2649.622803,2645.286133,2642.917725,2640.713867,2637.204590,2635.128906,2634.632324,2631.808594,2631.771729,2622.223633,2619.317383,2618.069336,2616.447754,2614.655273,2608.895264</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2679.659668,2676.791260,2675.209961,2674.581055,2671.773926,2670.283203,2670.491699,2667.521484,2669.544678,2665.457031,2661.444580,2660.958496,2660.936035,2654.877686,2656.880859,2656.879395,2654.909912,2653.204590,2650.246338,2647.906738,2646.989014,2642.271484,2642.035400,2637.920654</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3077,6 +3077,44 @@
       </c>
       <c r="F70" t="n">
         <v>2680.1044921875</v>
+      </c>
+      <c r="G70" t="n">
+        <v>2691.510009765625</v>
+      </c>
+      <c r="H70" t="n">
+        <v>11.405517578125</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.4237590622640183</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.197222349726936</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-27 05:02:26</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>24</v>
+      </c>
+      <c r="F71" t="n">
+        <v>2690.4716796875</v>
       </c>
     </row>
   </sheetData>
@@ -3090,7 +3128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7335,6 +7373,24 @@
           <t>2687.664062,2687.115723,2687.213135,2687.528320,2686.972168,2687.493408,2687.262939,2686.010986,2687.160889,2686.129639,2685.257080,2685.689453,2685.852051,2684.605957,2686.045410,2685.295654,2686.177734,2685.480469,2685.264893,2684.194824,2685.151123,2682.912109,2682.598633,2680.104492</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2686.149902,2685.060059,2690.439941,2690.429932,2682.219971,2686.919922,2688.989990,2688.399902,2686.229980,2688.540039,2692.500000,2691.010010,2690.000000,2684.620117,2683.959961,2676.250000,2685.909912,2688.149902,2695.689941,2692.899902,2701.110107,2697.300049,2695.870117,2691.510010</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>1.514160,2.055664,3.226806,2.901612,4.752197,0.573486,1.727051,2.388916,0.930909,2.410400,7.242920,5.320557,4.147949,0.014160,2.085449,9.045654,0.267822,2.669433,10.425048,8.705078,15.958984,14.387940,13.271484,11.405518</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>0.056369,0.076559,0.119936,0.107849,0.177174,0.021344,0.064227,0.088860,0.034655,0.089655,0.269004,0.197716,0.154199,0.000527,0.077700,0.337997,0.009971,0.099304,0.386730,0.323260,0.590831,0.533420,0.492289,0.423759</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>0.197222349726936</v>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>2682.612305,2685.500977,2687.326172,2681.082275,2688.514893,2685.236084,2684.377441,2681.090332,2684.940674,2682.128174,2682.203857,2678.068115,2680.087158,2680.740234,2680.901367,2678.145752,2680.697754,2680.491699,2679.937012,2673.132568,2675.779541,2676.539551,2677.989502,2673.056396</t>
@@ -7348,6 +7404,49 @@
       <c r="M70" t="inlineStr">
         <is>
           <t>2679.659668,2676.791260,2675.209961,2674.581055,2671.773926,2670.283203,2670.491699,2667.521484,2669.544678,2665.457031,2661.444580,2660.958496,2660.936035,2654.877686,2656.880859,2656.879395,2654.909912,2653.204590,2650.246338,2647.906738,2646.989014,2642.271484,2642.035400,2637.920654</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-09-27 05:02:26</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>24</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2692.647949,2691.887695,2691.982422,2693.056152,2692.230957,2693.177246,2693.717285,2692.843018,2692.824219,2693.645508,2693.189697,2693.549805,2693.437988,2692.523438,2693.265625,2693.250244,2693.155273,2693.908936,2691.944580,2693.096680,2693.166504,2692.150879,2692.063721,2690.471680</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>2690.753174,2691.975098,2690.543945,2687.656494,2693.604248,2691.374023,2691.735352,2688.391602,2692.397705,2690.136963,2689.822754,2686.392334,2686.458984,2688.580322,2686.863770,2684.596436,2689.120117,2689.109375,2688.794189,2682.427979,2683.355957,2684.138672,2687.043945,2682.332520</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2683.936768,2682.268066,2678.794678,2680.344238,2674.936279,2674.383545,2672.888672,2669.135010,2665.709473,2665.188721,2661.959717,2658.341309,2655.039551,2653.945557,2652.282471,2651.801758,2649.152832,2648.844238,2638.795410,2638.089600,2637.524414,2636.186035,2634.595215,2630.997070</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2689.352295,2687.070068,2685.950439,2685.646484,2683.079590,2681.614258,2681.648193,2679.674805,2680.474365,2677.901367,2674.093262,2673.881104,2674.885986,2670.499023,2670.887451,2672.635986,2671.824707,2669.609619,2665.687256,2665.366699,2663.236328,2660.121338,2660.413574,2657.207520</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3115,6 +3115,44 @@
       </c>
       <c r="F71" t="n">
         <v>2690.4716796875</v>
+      </c>
+      <c r="G71" t="n">
+        <v>2654.760009765625</v>
+      </c>
+      <c r="H71" t="n">
+        <v>35.711669921875</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1.345193907943031</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.650942816073426</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:04:11</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>24</v>
+      </c>
+      <c r="F72" t="n">
+        <v>2658.4482421875</v>
       </c>
     </row>
   </sheetData>
@@ -3128,7 +3166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7434,6 +7472,24 @@
           <t>2692.647949,2691.887695,2691.982422,2693.056152,2692.230957,2693.177246,2693.717285,2692.843018,2692.824219,2693.645508,2693.189697,2693.549805,2693.437988,2692.523438,2693.265625,2693.250244,2693.155273,2693.908936,2691.944580,2693.096680,2693.166504,2692.150879,2692.063721,2690.471680</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2706.479980,2717.709961,2713.409912,2715.360107,2709.550049,2709.080078,2706.760010,2709.370117,2687.399902,2689.500000,2685.899902,2690.590088,2697.639893,2690.929932,2685.530029,2684.070068,2675.239990,2687.949951,2673.790039,2656.719971,2651.790039,2651.790039,2657.969971,2654.760010</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>13.832031,25.822266,21.427490,22.303955,17.319092,15.902832,13.042725,16.527099,5.424317,4.145508,7.289795,2.959717,4.201905,1.593506,7.735596,9.180176,17.915283,5.958985,18.154541,36.376709,41.376465,40.360840,34.093750,35.711670</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>0.511071,0.950148,0.789689,0.821400,0.639187,0.587020,0.481857,0.609998,0.201843,0.154137,0.271410,0.110003,0.155762,0.059218,0.288047,0.342024,0.669670,0.221693,0.678982,1.369234,1.560322,1.522022,1.282699,1.345194</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>0.650942816073426</v>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>2690.753174,2691.975098,2690.543945,2687.656494,2693.604248,2691.374023,2691.735352,2688.391602,2692.397705,2690.136963,2689.822754,2686.392334,2686.458984,2688.580322,2686.863770,2684.596436,2689.120117,2689.109375,2688.794189,2682.427979,2683.355957,2684.138672,2687.043945,2682.332520</t>
@@ -7447,6 +7503,49 @@
       <c r="M71" t="inlineStr">
         <is>
           <t>2689.352295,2687.070068,2685.950439,2685.646484,2683.079590,2681.614258,2681.648193,2679.674805,2680.474365,2677.901367,2674.093262,2673.881104,2674.885986,2670.499023,2670.887451,2672.635986,2671.824707,2669.609619,2665.687256,2665.366699,2663.236328,2660.121338,2660.413574,2657.207520</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-09-28 05:04:11</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>24</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2654.412842,2654.416992,2654.244385,2655.048340,2654.522949,2654.577148,2656.450928,2655.253662,2654.744141,2656.201904,2656.651855,2657.204834,2659.096436,2658.196777,2659.312988,2659.013672,2660.263428,2660.301758,2659.963867,2660.091553,2659.339844,2659.142822,2659.297852,2658.448242</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>2652.658203,2655.433105,2654.442383,2652.457520,2657.763428,2656.525391,2657.889648,2651.039062,2657.599609,2656.192871,2655.426758,2656.723877,2654.737793,2656.643311,2656.470215,2655.948975,2658.693115,2660.158691,2660.412598,2654.060059,2654.316406,2652.066895,2658.791748,2655.709961</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2640.812988,2639.596191,2634.943115,2634.139893,2630.398193,2630.053223,2629.661133,2625.683838,2621.944336,2621.040527,2619.703857,2617.779053,2618.587402,2617.125732,2616.232666,2615.777100,2615.035156,2613.909180,2605.819336,2604.658447,2601.412354,2600.614014,2599.151367,2596.733398</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2647.077148,2645.018555,2643.216064,2641.369385,2639.418945,2638.368896,2639.425293,2636.313477,2637.365479,2634.547119,2632.941406,2634.489746,2636.650879,2632.972412,2635.412842,2635.790283,2635.945312,2632.240234,2631.383301,2629.554199,2626.341309,2624.855469,2624.391846,2622.596680</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3153,6 +3153,44 @@
       </c>
       <c r="F72" t="n">
         <v>2658.4482421875</v>
+      </c>
+      <c r="G72" t="n">
+        <v>2671.570068359375</v>
+      </c>
+      <c r="H72" t="n">
+        <v>13.121826171875</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.4911653385880754</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.639925218642845</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-29 05:28:56</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>24</v>
+      </c>
+      <c r="F73" t="n">
+        <v>2672.567138671875</v>
       </c>
     </row>
   </sheetData>
@@ -3166,7 +3204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7533,6 +7571,24 @@
           <t>2654.412842,2654.416992,2654.244385,2655.048340,2654.522949,2654.577148,2656.450928,2655.253662,2654.744141,2656.201904,2656.651855,2657.204834,2659.096436,2658.196777,2659.312988,2659.013672,2660.263428,2660.301758,2659.963867,2660.091553,2659.339844,2659.142822,2659.297852,2658.448242</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2649.000000,2642.879883,2649.669922,2639.750000,2654.939941,2667.989990,2690.219971,2689.860107,2666.530029,2677.870117,2686.139893,2694.530029,2698.639893,2672.409912,2681.639893,2673.159912,2686.469971,2687.350098,2676.040039,2664.370117,2656.370117,2664.159912,2666.689941,2671.570068</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>5.412842,11.537109,4.574463,15.298340,0.416992,13.412842,33.769043,34.606445,11.785888,21.668213,29.488038,37.325195,39.543457,14.213135,22.326905,14.146240,26.206543,27.048340,16.076172,4.278564,2.969727,5.017090,7.392089,13.121826</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>0.204335,0.436536,0.172643,0.579537,0.015706,0.502732,1.255252,1.286552,0.441993,0.809158,1.097785,1.385221,1.465311,0.531847,0.832584,0.529195,0.975501,1.006506,0.600745,0.160584,0.111796,0.188318,0.277201,0.491165</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>0.639925218642845</v>
+      </c>
       <c r="K72" t="inlineStr">
         <is>
           <t>2652.658203,2655.433105,2654.442383,2652.457520,2657.763428,2656.525391,2657.889648,2651.039062,2657.599609,2656.192871,2655.426758,2656.723877,2654.737793,2656.643311,2656.470215,2655.948975,2658.693115,2660.158691,2660.412598,2654.060059,2654.316406,2652.066895,2658.791748,2655.709961</t>
@@ -7546,6 +7602,49 @@
       <c r="M72" t="inlineStr">
         <is>
           <t>2647.077148,2645.018555,2643.216064,2641.369385,2639.418945,2638.368896,2639.425293,2636.313477,2637.365479,2634.547119,2632.941406,2634.489746,2636.650879,2632.972412,2635.412842,2635.790283,2635.945312,2632.240234,2631.383301,2629.554199,2626.341309,2624.855469,2624.391846,2622.596680</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-09-29 05:28:56</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>24</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2669.582520,2670.304932,2670.610840,2672.365234,2672.997803,2673.498047,2674.671387,2674.021484,2673.540771,2673.854248,2673.286133,2673.709961,2675.564453,2674.002197,2674.267334,2674.534668,2675.115234,2673.500244,2673.601562,2674.370605,2673.985596,2673.330078,2672.970215,2672.567139</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>2668.454834,2672.764160,2671.277344,2670.088623,2676.127930,2674.806641,2675.355713,2672.304443,2674.215088,2674.319336,2672.634033,2672.721680,2673.065674,2673.804443,2672.601562,2673.427002,2671.667969,2673.280273,2673.606201,2668.283936,2669.971680,2668.635742,2674.018066,2668.462158</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2655.988525,2654.745850,2650.631836,2650.433838,2648.781982,2647.512207,2646.914551,2643.964355,2640.027832,2637.574707,2636.708252,2634.530029,2633.864746,2631.395996,2631.439697,2629.618164,2628.390625,2626.520264,2620.146484,2620.099854,2618.647461,2617.688965,2615.059814,2613.116455</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2662.156494,2660.369385,2658.584473,2658.509277,2657.545166,2656.223877,2657.012939,2654.840088,2654.531494,2651.182861,2649.373047,2650.579834,2652.009521,2646.627197,2649.087158,2649.316162,2647.329590,2643.851318,2642.714844,2642.474609,2640.733887,2639.055908,2638.818848,2637.545166</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3191,6 +3191,44 @@
       </c>
       <c r="F73" t="n">
         <v>2672.567138671875</v>
+      </c>
+      <c r="G73" t="n">
+        <v>2666.510009765625</v>
+      </c>
+      <c r="H73" t="n">
+        <v>6.05712890625</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.2271556785486208</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.75341155419334</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-30 05:16:32</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>24</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2669.2822265625</v>
       </c>
     </row>
   </sheetData>
@@ -3204,7 +3242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7632,6 +7670,24 @@
           <t>2669.582520,2670.304932,2670.610840,2672.365234,2672.997803,2673.498047,2674.671387,2674.021484,2673.540771,2673.854248,2673.286133,2673.709961,2675.564453,2674.002197,2674.267334,2674.534668,2675.115234,2673.500244,2673.601562,2674.370605,2673.985596,2673.330078,2672.970215,2672.567139</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2705.719971,2711.100098,2708.389893,2716.620117,2713.649902,2731.250000,2736.139893,2726.939941,2709.939941,2673.219971,2674.979980,2672.830078,2694.739990,2688.310059,2688.429932,2678.250000,2680.649902,2677.060059,2671.280029,2671.080078,2673.320068,2670.979980,2668.810059,2666.510010</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>36.137451,40.795166,37.779053,44.254883,40.652099,57.751953,61.468506,52.918457,36.399170,0.634277,1.693847,0.879883,19.175537,14.307862,14.162598,3.715332,5.534668,3.559815,2.321533,3.290527,0.665528,2.350098,4.160156,6.057129</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1.335595,1.504746,1.394890,1.629042,1.498060,2.114488,2.246541,1.940580,1.343173,0.023727,0.063322,0.032920,0.711591,0.532225,0.526798,0.138722,0.206467,0.132975,0.086907,0.123191,0.024895,0.087986,0.155881,0.227156</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>0.75341155419334</v>
+      </c>
       <c r="K73" t="inlineStr">
         <is>
           <t>2668.454834,2672.764160,2671.277344,2670.088623,2676.127930,2674.806641,2675.355713,2672.304443,2674.215088,2674.319336,2672.634033,2672.721680,2673.065674,2673.804443,2672.601562,2673.427002,2671.667969,2673.280273,2673.606201,2668.283936,2669.971680,2668.635742,2674.018066,2668.462158</t>
@@ -7645,6 +7701,49 @@
       <c r="M73" t="inlineStr">
         <is>
           <t>2662.156494,2660.369385,2658.584473,2658.509277,2657.545166,2656.223877,2657.012939,2654.840088,2654.531494,2651.182861,2649.373047,2650.579834,2652.009521,2646.627197,2649.087158,2649.316162,2647.329590,2643.851318,2642.714844,2642.474609,2640.733887,2639.055908,2638.818848,2637.545166</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-09-30 05:16:32</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>24</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2666.876221,2666.580078,2667.129639,2667.921143,2668.463379,2668.973389,2669.889893,2668.639160,2667.993896,2668.168701,2667.189941,2667.609619,2668.755859,2667.702393,2668.749756,2668.953857,2669.964600,2669.537598,2669.615479,2670.266357,2669.758057,2669.727783,2668.801025,2669.282227</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>2666.278076,2669.455078,2666.849365,2666.960693,2669.369629,2670.066162,2670.423828,2664.217285,2667.834717,2670.114258,2666.097656,2665.910889,2666.173096,2667.943359,2666.829346,2668.342773,2668.470703,2667.814453,2670.027832,2665.510498,2665.968262,2665.347412,2670.149902,2666.650879</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2654.617676,2652.377686,2648.715088,2647.950195,2645.502930,2645.217041,2644.282471,2640.144531,2638.069092,2635.848877,2634.260254,2631.110840,2631.516113,2629.498535,2629.765625,2628.340820,2628.715332,2627.643066,2621.024414,2620.522217,2619.325928,2617.945068,2615.584961,2615.687988</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2660.178223,2657.524170,2656.111328,2655.405029,2654.028564,2653.181396,2654.077881,2650.358154,2651.113770,2647.157471,2645.132080,2646.852051,2646.969238,2643.408203,2645.760986,2645.724609,2646.176758,2642.822021,2641.958496,2640.802246,2638.866943,2638.013672,2636.831299,2635.975830</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3229,6 +3229,44 @@
       </c>
       <c r="F74" t="n">
         <v>2669.2822265625</v>
+      </c>
+      <c r="G74" t="n">
+        <v>2712.199951171875</v>
+      </c>
+      <c r="H74" t="n">
+        <v>42.917724609375</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1.58239530204369</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.7254530412490134</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-10-01 05:31:41</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>24</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2694.807861328125</v>
       </c>
     </row>
   </sheetData>
@@ -3242,7 +3280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7731,6 +7769,24 @@
           <t>2666.876221,2666.580078,2667.129639,2667.921143,2668.463379,2668.973389,2669.889893,2668.639160,2667.993896,2668.168701,2667.189941,2667.609619,2668.755859,2667.702393,2668.749756,2668.953857,2669.964600,2669.537598,2669.615479,2670.266357,2669.758057,2669.727783,2668.801025,2669.282227</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2660.739990,2673.610107,2669.820068,2687.389893,2694.270020,2696.709961,2730.590088,2708.580078,2676.739990,2681.780029,2694.290039,2681.860107,2677.989990,2668.870117,2680.889893,2682.870117,2685.360107,2683.929932,2683.040039,2688.050049,2685.330078,2693.729980,2705.370117,2712.199951</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>6.136231,7.030029,2.690429,19.468750,25.806641,27.736572,60.700195,39.940918,8.746094,13.611328,27.100098,14.250488,9.234131,1.167724,12.140137,13.916260,15.395507,14.392334,13.424560,17.783692,15.572021,24.002197,36.569092,42.917724</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>0.230621,0.262941,0.100772,0.724448,0.957834,1.028534,2.222970,1.474607,0.326744,0.507548,1.005834,0.531366,0.344816,0.043754,0.452840,0.518708,0.573313,0.536241,0.500349,0.661583,0.579892,0.891039,1.351722,1.582395</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>0.7254530412490134</v>
+      </c>
       <c r="K74" t="inlineStr">
         <is>
           <t>2666.278076,2669.455078,2666.849365,2666.960693,2669.369629,2670.066162,2670.423828,2664.217285,2667.834717,2670.114258,2666.097656,2665.910889,2666.173096,2667.943359,2666.829346,2668.342773,2668.470703,2667.814453,2670.027832,2665.510498,2665.968262,2665.347412,2670.149902,2666.650879</t>
@@ -7744,6 +7800,49 @@
       <c r="M74" t="inlineStr">
         <is>
           <t>2660.178223,2657.524170,2656.111328,2655.405029,2654.028564,2653.181396,2654.077881,2650.358154,2651.113770,2647.157471,2645.132080,2646.852051,2646.969238,2643.408203,2645.760986,2645.724609,2646.176758,2642.822021,2641.958496,2640.802246,2638.866943,2638.013672,2636.831299,2635.975830</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-10-01 05:31:41</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>24</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2709.705811,2707.630127,2706.964844,2705.777344,2705.607422,2705.753906,2705.573486,2703.484375,2702.978760,2703.343994,2700.760986,2700.778809,2700.381104,2698.449219,2699.026611,2697.624756,2698.891846,2697.963867,2696.923584,2697.286133,2695.839355,2694.533203,2693.601074,2694.807861</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>2709.969971,2710.123291,2707.057373,2706.202148,2707.651367,2705.832275,2705.114014,2703.495605,2702.786133,2702.741211,2699.987549,2698.320068,2697.667480,2698.292480,2698.897217,2697.210449,2697.422852,2696.252686,2697.370850,2693.922119,2693.549316,2693.113037,2694.031006,2692.541748</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2692.879883,2687.455322,2681.870850,2678.961426,2675.592773,2673.724609,2671.827637,2667.005127,2664.445557,2662.866211,2660.115967,2657.125244,2656.119385,2652.527100,2652.569580,2648.936035,2650.080078,2648.850098,2643.884521,2642.158203,2639.982178,2636.982666,2635.124268,2634.765625</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2699.969482,2695.140625,2691.892090,2689.331543,2686.245361,2684.827393,2683.825195,2679.844971,2678.977295,2677.209961,2673.412109,2674.047852,2673.170410,2668.870605,2670.787598,2669.225098,2669.429199,2668.275391,2666.269043,2665.477539,2663.140381,2660.754883,2660.179688,2660.688721</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3267,6 +3267,44 @@
       </c>
       <c r="F75" t="n">
         <v>2694.807861328125</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2732.5</v>
+      </c>
+      <c r="H75" t="n">
+        <v>37.692138671875</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1.379401232273559</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.5149552937627435</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-10-02 05:19:16</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>24</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2719.80517578125</v>
       </c>
     </row>
   </sheetData>
@@ -3280,7 +3318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7830,6 +7868,24 @@
           <t>2709.705811,2707.630127,2706.964844,2705.777344,2705.607422,2705.753906,2705.573486,2703.484375,2702.978760,2703.343994,2700.760986,2700.778809,2700.381104,2698.449219,2699.026611,2697.624756,2698.891846,2697.963867,2696.923584,2697.286133,2695.839355,2694.533203,2693.601074,2694.807861</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2713.909912,2676.239990,2685.840088,2689.830078,2700.520020,2705.760010,2692.260010,2697.419922,2689.189941,2681.750000,2679.120117,2700.199951,2699.159912,2698.550049,2697.580078,2692.520020,2702.000000,2705.500000,2706.659912,2714.629883,2719.889893,2718.570068,2741.979980,2732.500000</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.204101,31.390137,21.124756,15.947266,5.087402,0.006104,13.313476,6.064453,13.788819,21.593994,21.640869,0.578858,1.221192,0.100830,1.446533,5.104736,3.108154,7.536133,9.736328,17.343750,24.050538,24.036865,48.378906,37.692139</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>0.154909,1.172919,0.786523,0.592873,0.188386,0.000226,0.494509,0.224824,0.512750,0.805220,0.807760,0.021438,0.045243,0.003736,0.053623,0.189590,0.115032,0.278549,0.359717,0.638899,0.884247,0.884173,1.764379,1.379401</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>0.5149552937627435</v>
+      </c>
       <c r="K75" t="inlineStr">
         <is>
           <t>2709.969971,2710.123291,2707.057373,2706.202148,2707.651367,2705.832275,2705.114014,2703.495605,2702.786133,2702.741211,2699.987549,2698.320068,2697.667480,2698.292480,2698.897217,2697.210449,2697.422852,2696.252686,2697.370850,2693.922119,2693.549316,2693.113037,2694.031006,2692.541748</t>
@@ -7843,6 +7899,49 @@
       <c r="M75" t="inlineStr">
         <is>
           <t>2699.969482,2695.140625,2691.892090,2689.331543,2686.245361,2684.827393,2683.825195,2679.844971,2678.977295,2677.209961,2673.412109,2674.047852,2673.170410,2668.870605,2670.787598,2669.225098,2669.429199,2668.275391,2666.269043,2665.477539,2663.140381,2660.754883,2660.179688,2660.688721</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-10-02 05:19:16</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>24</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2728.167725,2725.929688,2725.109863,2724.529785,2723.833008,2724.112305,2724.250732,2722.320068,2722.677246,2722.609375,2722.272217,2721.909668,2721.254395,2719.500977,2720.177490,2719.368896,2721.308594,2720.514160,2719.655762,2719.537354,2719.935791,2719.998779,2720.154541,2719.805176</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>2728.313477,2726.470215,2724.092773,2724.717285,2724.613770,2723.852051,2722.230469,2723.499756,2721.289062,2722.060303,2720.399902,2718.410400,2717.223633,2718.245361,2717.120605,2716.207275,2719.241699,2714.524658,2716.802002,2714.559082,2716.345459,2714.851318,2716.288818,2715.156494</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2710.802002,2706.294434,2701.930420,2700.113525,2697.245605,2695.656250,2693.729736,2689.585693,2688.987549,2687.259766,2685.935303,2682.405029,2681.339844,2679.239258,2677.405273,2675.185547,2677.555420,2676.228271,2671.245850,2669.294189,2669.429688,2668.843750,2668.006348,2667.226562</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2718.077881,2713.695557,2710.839844,2709.777588,2706.465088,2705.193848,2704.491455,2701.536865,2701.833252,2699.796631,2697.839600,2697.343506,2697.094727,2693.498779,2694.037598,2693.234619,2695.465820,2693.661133,2691.423584,2690.169189,2689.668701,2689.242920,2689.329346,2688.894043</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3305,6 +3305,44 @@
       </c>
       <c r="F76" t="n">
         <v>2719.80517578125</v>
+      </c>
+      <c r="G76" t="n">
+        <v>2673.800048828125</v>
+      </c>
+      <c r="H76" t="n">
+        <v>46.005126953125</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1.720589651918368</v>
+      </c>
+      <c r="J76" t="n">
+        <v>1.31655917397916</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-10-03 05:02:06</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>24</v>
+      </c>
+      <c r="F77" t="n">
+        <v>2681.9091796875</v>
       </c>
     </row>
   </sheetData>
@@ -3318,7 +3356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7929,6 +7967,24 @@
           <t>2728.167725,2725.929688,2725.109863,2724.529785,2723.833008,2724.112305,2724.250732,2722.320068,2722.677246,2722.609375,2722.272217,2721.909668,2721.254395,2719.500977,2720.177490,2719.368896,2721.308594,2720.514160,2719.655762,2719.537354,2719.935791,2719.998779,2720.154541,2719.805176</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2728.110107,2736.229980,2753.090088,2746.570068,2742.620117,2746.199951,2755.010010,2744.280029,2709.340088,2696.929932,2689.669922,2683.949951,2664.399902,2667.290039,2661.209961,2664.810059,2667.530029,2668.139893,2675.949951,2678.969971,2676.520020,2681.610107,2675.530029,2673.800049</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>0.057618,10.300292,27.980225,22.040283,18.787109,22.087646,30.759278,21.959961,13.337158,25.679443,32.602295,37.959717,56.854493,52.210938,58.967529,54.558837,53.778565,52.374267,43.705811,40.567383,43.415771,38.388672,44.624512,46.005127</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>0.002112,0.376441,1.016321,0.802466,0.685006,0.804299,1.116485,0.800208,0.492266,0.952173,1.212130,1.414323,2.133857,1.957453,2.215816,2.047382,2.016043,1.962951,1.633282,1.514290,1.622098,1.431553,1.667876,1.720590</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>1.31655917397916</v>
+      </c>
       <c r="K76" t="inlineStr">
         <is>
           <t>2728.313477,2726.470215,2724.092773,2724.717285,2724.613770,2723.852051,2722.230469,2723.499756,2721.289062,2722.060303,2720.399902,2718.410400,2717.223633,2718.245361,2717.120605,2716.207275,2719.241699,2714.524658,2716.802002,2714.559082,2716.345459,2714.851318,2716.288818,2715.156494</t>
@@ -7942,6 +7998,49 @@
       <c r="M76" t="inlineStr">
         <is>
           <t>2718.077881,2713.695557,2710.839844,2709.777588,2706.465088,2705.193848,2704.491455,2701.536865,2701.833252,2699.796631,2697.839600,2697.343506,2697.094727,2693.498779,2694.037598,2693.234619,2695.465820,2693.661133,2691.423584,2690.169189,2689.668701,2689.242920,2689.329346,2688.894043</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-10-03 05:02:06</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>24</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2675.368408,2675.322998,2675.862061,2676.603027,2676.816162,2677.150146,2678.131104,2677.141846,2677.214111,2676.201172,2676.644531,2676.316406,2676.439697,2675.613770,2676.639404,2677.548584,2679.395508,2679.987061,2680.656250,2680.553711,2680.647705,2681.434082,2681.851074,2681.909180</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>2675.469727,2676.415039,2674.491455,2676.184570,2676.633057,2678.345947,2676.392090,2675.926758,2677.558838,2677.210938,2675.284180,2674.218994,2673.701172,2675.850586,2673.227539,2674.961426,2677.147217,2677.861816,2678.312500,2676.440186,2678.430664,2676.349854,2679.798828,2678.398438</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2664.442383,2662.259766,2659.617188,2658.944824,2655.268311,2653.416260,2653.299072,2649.486084,2646.931641,2644.224121,2642.962891,2642.493408,2640.673340,2639.419678,2637.840088,2637.832520,2639.243164,2638.916748,2635.904541,2634.216553,2632.817871,2633.054199,2632.342529,2631.565186</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2669.904541,2667.395020,2666.364746,2665.458740,2663.220703,2662.055176,2662.135498,2659.440430,2660.036133,2656.958008,2655.482178,2655.880127,2656.066406,2654.006348,2654.446533,2655.393066,2656.273682,2655.405273,2655.429688,2655.116943,2653.857178,2652.563477,2652.946045,2652.666992</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3343,6 +3343,44 @@
       </c>
       <c r="F77" t="n">
         <v>2681.9091796875</v>
+      </c>
+      <c r="G77" t="n">
+        <v>2694.2099609375</v>
+      </c>
+      <c r="H77" t="n">
+        <v>12.30078125</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.4565635725628346</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.2953827295276432</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-10-04 05:34:28</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>24</v>
+      </c>
+      <c r="F78" t="n">
+        <v>2694.457763671875</v>
       </c>
     </row>
   </sheetData>
@@ -3356,7 +3394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M77"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8028,6 +8066,24 @@
           <t>2675.368408,2675.322998,2675.862061,2676.603027,2676.816162,2677.150146,2678.131104,2677.141846,2677.214111,2676.201172,2676.644531,2676.316406,2676.439697,2675.613770,2676.639404,2677.548584,2679.395508,2679.987061,2680.656250,2680.553711,2680.647705,2681.434082,2681.851074,2681.909180</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2679.699951,2681.610107,2682.429932,2680.050049,2682.820068,2684.010010,2682.209961,2681.530029,2683.050049,2681.219971,2681.040039,2688.419922,2684.810059,2685.189941,2686.449951,2685.030029,2686.159912,2686.939941,2692.659912,2694.320068,2692.189941,2694.030029,2691.899902,2694.209961</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>4.331543,6.287109,6.567871,3.447022,6.003906,6.859864,4.078857,4.388183,5.835938,5.018799,4.395508,12.103516,8.370362,9.576171,9.810547,7.481445,6.764404,6.952880,12.003662,13.766357,11.542236,12.595947,10.048828,12.300781</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>0.161643,0.234453,0.244848,0.128618,0.223791,0.255583,0.152071,0.163645,0.217511,0.187183,0.163948,0.450209,0.311767,0.356629,0.365186,0.278635,0.251824,0.258766,0.445792,0.510940,0.428730,0.467550,0.373299,0.456564</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>0.2953827295276432</v>
+      </c>
       <c r="K77" t="inlineStr">
         <is>
           <t>2675.469727,2676.415039,2674.491455,2676.184570,2676.633057,2678.345947,2676.392090,2675.926758,2677.558838,2677.210938,2675.284180,2674.218994,2673.701172,2675.850586,2673.227539,2674.961426,2677.147217,2677.861816,2678.312500,2676.440186,2678.430664,2676.349854,2679.798828,2678.398438</t>
@@ -8041,6 +8097,49 @@
       <c r="M77" t="inlineStr">
         <is>
           <t>2669.904541,2667.395020,2666.364746,2665.458740,2663.220703,2662.055176,2662.135498,2659.440430,2660.036133,2656.958008,2655.482178,2655.880127,2656.066406,2654.006348,2654.446533,2655.393066,2656.273682,2655.405273,2655.429688,2655.116943,2653.857178,2652.563477,2652.946045,2652.666992</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-10-04 05:34:28</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>24</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2693.835449,2693.749023,2694.452637,2695.072998,2695.606445,2696.371582,2696.814941,2696.068115,2696.480713,2695.962891,2696.699219,2696.525146,2696.199951,2694.929932,2695.241699,2695.206543,2695.644287,2694.565186,2695.094238,2694.616211,2694.613281,2694.255859,2694.497314,2694.457764</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>2692.547852,2695.019287,2693.716797,2694.428223,2694.310059,2696.637939,2696.414307,2695.975586,2696.969482,2695.924561,2694.095215,2694.105957,2693.070312,2694.505127,2693.897461,2691.535156,2692.001953,2691.381592,2692.942139,2690.609863,2691.083496,2690.097900,2690.955811,2690.913330</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2686.995850,2686.399902,2684.964111,2685.124512,2682.199707,2682.124268,2680.397705,2676.519043,2674.951904,2672.588135,2671.703125,2670.205811,2667.571289,2665.877441,2665.409912,2664.055176,2663.060303,2661.034424,2657.504639,2658.039062,2656.905518,2655.691895,2655.706299,2654.353271</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2690.943115,2689.531738,2689.125000,2688.900879,2687.531006,2687.457031,2686.947510,2685.071777,2685.392334,2683.305664,2682.125977,2681.330811,2680.593262,2677.916748,2678.753418,2678.659424,2677.749512,2675.217285,2674.897461,2674.939453,2674.438477,2672.152588,2672.903320,2672.572021</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3381,6 +3381,44 @@
       </c>
       <c r="F78" t="n">
         <v>2694.457763671875</v>
+      </c>
+      <c r="G78" t="n">
+        <v>2697.179931640625</v>
+      </c>
+      <c r="H78" t="n">
+        <v>2.72216796875</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.1009264505054424</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.4272551890900794</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-10-05 05:18:12</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>24</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2690.926025390625</v>
       </c>
     </row>
   </sheetData>
@@ -3394,7 +3432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8127,6 +8165,24 @@
           <t>2693.835449,2693.749023,2694.452637,2695.072998,2695.606445,2696.371582,2696.814941,2696.068115,2696.480713,2695.962891,2696.699219,2696.525146,2696.199951,2694.929932,2695.241699,2695.206543,2695.644287,2694.565186,2695.094238,2694.616211,2694.613281,2694.255859,2694.497314,2694.457764</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2695.679932,2706.010010,2699.969971,2701.290039,2700.919922,2699.860107,2694.860107,2698.959961,2697.439941,2698.530029,2702.979980,2701.709961,2700.520020,2701.129883,2705.500000,2701.840088,2730.310059,2726.669922,2728.810059,2723.919922,2730.639893,2715.209961,2701.870117,2697.179932</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>1.844483,12.260987,5.517334,6.217041,5.313477,3.488525,1.954834,2.891846,0.959228,2.567138,6.280761,5.184815,4.320069,6.199951,10.258301,6.633545,34.665772,32.104736,33.715821,29.303711,36.026612,20.954102,7.372803,2.722168</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>0.068424,0.453102,0.204348,0.230151,0.196728,0.129211,0.072539,0.107147,0.035561,0.095131,0.232364,0.191909,0.159972,0.229532,0.379165,0.245520,1.269664,1.177434,1.235550,1.075792,1.319347,0.771730,0.272878,0.100926</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>0.4272551890900794</v>
+      </c>
       <c r="K78" t="inlineStr">
         <is>
           <t>2692.547852,2695.019287,2693.716797,2694.428223,2694.310059,2696.637939,2696.414307,2695.975586,2696.969482,2695.924561,2694.095215,2694.105957,2693.070312,2694.505127,2693.897461,2691.535156,2692.001953,2691.381592,2692.942139,2690.609863,2691.083496,2690.097900,2690.955811,2690.913330</t>
@@ -8140,6 +8196,49 @@
       <c r="M78" t="inlineStr">
         <is>
           <t>2690.943115,2689.531738,2689.125000,2688.900879,2687.531006,2687.457031,2686.947510,2685.071777,2685.392334,2683.305664,2682.125977,2681.330811,2680.593262,2677.916748,2678.753418,2678.659424,2677.749512,2675.217285,2674.897461,2674.939453,2674.438477,2672.152588,2672.903320,2672.572021</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-10-05 05:18:12</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>24</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2696.608398,2694.645020,2693.958984,2694.624023,2693.158203,2693.777832,2693.739746,2693.300293,2693.609863,2693.263672,2692.802490,2693.158691,2692.723389,2691.971924,2693.320801,2693.614502,2693.471680,2692.603271,2693.077637,2692.660889,2693.160400,2692.291748,2691.570801,2690.926025</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>2695.430176,2694.863281,2692.802246,2695.310303,2694.062988,2691.980225,2692.516113,2691.548096,2691.085205,2691.919922,2690.900391,2688.937988,2688.709717,2691.748535,2689.879639,2689.178467,2690.039307,2688.487549,2689.190186,2687.586426,2687.524170,2687.998047,2686.930420,2686.343506</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2685.800537,2682.434082,2678.578369,2677.812988,2673.795166,2672.610107,2670.631104,2668.593750,2666.583008,2664.200195,2661.845215,2661.282715,2659.137939,2658.631592,2658.046631,2656.833008,2655.450439,2653.635742,2650.939941,2649.264648,2649.104492,2648.214355,2647.160889,2645.491699</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2691.038574,2687.109619,2684.967529,2684.182129,2681.211670,2680.041016,2679.570801,2678.156982,2678.595459,2676.387451,2673.705811,2674.202148,2673.373535,2671.776611,2673.039795,2673.299316,2671.972168,2670.103516,2669.508301,2668.825195,2668.698242,2666.910156,2666.278809,2665.809082</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3419,6 +3419,44 @@
       </c>
       <c r="F79" t="n">
         <v>2690.926025390625</v>
+      </c>
+      <c r="G79" t="n">
+        <v>2698.590087890625</v>
+      </c>
+      <c r="H79" t="n">
+        <v>7.6640625</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.284002469822702</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.6405686318377779</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:02:20</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>24</v>
+      </c>
+      <c r="F80" t="n">
+        <v>2695.97900390625</v>
       </c>
     </row>
   </sheetData>
@@ -3432,7 +3470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8226,6 +8264,24 @@
           <t>2696.608398,2694.645020,2693.958984,2694.624023,2693.158203,2693.777832,2693.739746,2693.300293,2693.609863,2693.263672,2692.802490,2693.158691,2692.723389,2691.971924,2693.320801,2693.614502,2693.471680,2692.603271,2693.077637,2692.660889,2693.160400,2692.291748,2691.570801,2690.926025</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2725.010010,2725.419922,2720.580078,2716.919922,2716.929932,2717.760010,2710.409912,2722.260010,2703.669922,2696.770020,2695.979980,2705.199951,2710.199951,2708.419922,2711.840088,2717.610107,2715.580078,2709.560059,2718.270020,2707.060059,2701.439941,2698.219971,2701.699951,2698.590088</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>28.401612,30.774902,26.621094,22.295899,23.771729,23.982178,16.670166,28.959717,10.060059,3.506348,3.177490,12.041260,17.476562,16.447998,18.519287,23.995605,22.108398,16.956788,25.192383,14.399170,8.279541,5.928223,10.129150,7.664063</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1.042257,1.129180,0.978508,0.820631,0.874948,0.882424,0.615042,1.063812,0.372089,0.130020,0.117860,0.445115,0.644844,0.607291,0.682905,0.882967,0.814132,0.625813,0.926780,0.531912,0.306486,0.219709,0.374918,0.284002</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>0.6405686318377779</v>
+      </c>
       <c r="K79" t="inlineStr">
         <is>
           <t>2695.430176,2694.863281,2692.802246,2695.310303,2694.062988,2691.980225,2692.516113,2691.548096,2691.085205,2691.919922,2690.900391,2688.937988,2688.709717,2691.748535,2689.879639,2689.178467,2690.039307,2688.487549,2689.190186,2687.586426,2687.524170,2687.998047,2686.930420,2686.343506</t>
@@ -8239,6 +8295,49 @@
       <c r="M79" t="inlineStr">
         <is>
           <t>2691.038574,2687.109619,2684.967529,2684.182129,2681.211670,2680.041016,2679.570801,2678.156982,2678.595459,2676.387451,2673.705811,2674.202148,2673.373535,2671.776611,2673.039795,2673.299316,2671.972168,2670.103516,2669.508301,2668.825195,2668.698242,2666.910156,2666.278809,2665.809082</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:02:20</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>24</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2695.845703,2695.360352,2695.395752,2696.610840,2696.721680,2697.229736,2697.050293,2696.904297,2696.819824,2696.764160,2695.895752,2696.143555,2696.105469,2695.759277,2696.490479,2696.791260,2697.353271,2696.629639,2696.917725,2696.575195,2696.959473,2696.426025,2695.640381,2695.979004</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>2695.073975,2695.160400,2694.931152,2698.510254,2698.868652,2695.352783,2696.474854,2694.531982,2695.359375,2693.556885,2695.035889,2693.129395,2691.668213,2695.282715,2693.367432,2692.395020,2694.603271,2693.415039,2694.530273,2691.336182,2691.737305,2692.893555,2691.568848,2690.836914</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2687.275391,2685.796631,2683.274414,2683.328125,2681.519531,2680.009766,2678.476562,2676.477539,2674.185303,2672.550049,2669.963135,2669.151855,2667.156738,2666.788574,2665.197754,2664.604736,2663.798340,2662.493164,2659.514404,2657.682373,2657.319336,2657.304199,2656.224609,2655.457520</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2691.656982,2689.629395,2688.462646,2688.692139,2687.449463,2686.249512,2685.646240,2684.887451,2684.359131,2683.395508,2680.258545,2680.653320,2680.104248,2678.877441,2679.116943,2679.663574,2678.522461,2677.694092,2677.017578,2676.407959,2676.487549,2674.705322,2674.127686,2674.728271</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3457,6 +3457,44 @@
       </c>
       <c r="F80" t="n">
         <v>2695.97900390625</v>
+      </c>
+      <c r="G80" t="n">
+        <v>2616.550048828125</v>
+      </c>
+      <c r="H80" t="n">
+        <v>79.428955078125</v>
+      </c>
+      <c r="I80" t="n">
+        <v>3.035636758169364</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.9810535269471532</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-10-07 05:37:31</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>24</v>
+      </c>
+      <c r="F81" t="n">
+        <v>2629.6962890625</v>
       </c>
     </row>
   </sheetData>
@@ -3470,7 +3508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8325,6 +8363,24 @@
           <t>2695.845703,2695.360352,2695.395752,2696.610840,2696.721680,2697.229736,2697.050293,2696.904297,2696.819824,2696.764160,2695.895752,2696.143555,2696.105469,2695.759277,2696.490479,2696.791260,2697.353271,2696.629639,2696.917725,2696.575195,2696.959473,2696.426025,2695.640381,2695.979004</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2706.800049,2715.870117,2709.760010,2713.090088,2713.620117,2715.290039,2714.449951,2722.409912,2702.399902,2695.360107,2699.189941,2690.000000,2691.739990,2698.270020,2698.159912,2696.260010,2697.280029,2696.389893,2657.310059,2611.770020,2610.530029,2609.830078,2616.550049,2616.550049</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>10.954346,20.509765,14.364258,16.479248,16.898437,18.060303,17.399658,25.505615,5.580078,1.404053,3.294189,6.143555,4.365479,2.510743,1.669433,0.531250,0.073242,0.239746,39.607666,84.805175,86.429444,86.595947,79.090332,79.428955</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>0.404697,0.755182,0.530093,0.607398,0.622727,0.665133,0.641001,0.936876,0.206486,0.052091,0.122044,0.228385,0.162181,0.093050,0.061873,0.019703,0.002715,0.008891,1.490517,3.247038,3.310801,3.318068,3.022695,3.035637</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>0.9810535269471532</v>
+      </c>
       <c r="K80" t="inlineStr">
         <is>
           <t>2695.073975,2695.160400,2694.931152,2698.510254,2698.868652,2695.352783,2696.474854,2694.531982,2695.359375,2693.556885,2695.035889,2693.129395,2691.668213,2695.282715,2693.367432,2692.395020,2694.603271,2693.415039,2694.530273,2691.336182,2691.737305,2692.893555,2691.568848,2690.836914</t>
@@ -8338,6 +8394,49 @@
       <c r="M80" t="inlineStr">
         <is>
           <t>2691.656982,2689.629395,2688.462646,2688.692139,2687.449463,2686.249512,2685.646240,2684.887451,2684.359131,2683.395508,2680.258545,2680.653320,2680.104248,2678.877441,2679.116943,2679.663574,2678.522461,2677.694092,2677.017578,2676.407959,2676.487549,2674.705322,2674.127686,2674.728271</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-10-07 05:37:31</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>24</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2618.074707,2617.949219,2618.990479,2620.362793,2621.037354,2622.362061,2622.535889,2621.193115,2621.126953,2622.045410,2621.487305,2622.362793,2623.988525,2623.908447,2625.387939,2626.036621,2627.977051,2628.131836,2629.533447,2628.958984,2629.551758,2630.001953,2629.766846,2629.696289</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>2617.733154,2620.394043,2619.939697,2623.072510,2623.275146,2623.920898,2624.219971,2622.112793,2622.322754,2622.193848,2622.860352,2624.614258,2623.211670,2624.654785,2625.150391,2622.911133,2626.169189,2627.363037,2627.479004,2626.092041,2627.390381,2623.437256,2625.868652,2625.049072</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2598.174072,2593.588867,2588.918457,2586.549805,2582.951172,2579.245850,2578.290771,2573.955811,2569.518555,2566.871582,2563.296631,2563.912842,2562.669189,2562.666748,2561.522461,2560.352539,2561.427002,2559.995850,2556.246338,2553.321045,2552.630371,2552.760254,2551.739258,2549.587158</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2607.321045,2603.148193,2600.191650,2599.215332,2597.103516,2595.414551,2593.614014,2591.076660,2589.803223,2588.280273,2584.581543,2585.843018,2586.658691,2585.708984,2586.866943,2586.392090,2587.471191,2586.526855,2586.495117,2585.808838,2585.367920,2584.298584,2583.410889,2583.857178</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3495,6 +3495,44 @@
       </c>
       <c r="F81" t="n">
         <v>2629.6962890625</v>
+      </c>
+      <c r="G81" t="n">
+        <v>2568.080078125</v>
+      </c>
+      <c r="H81" t="n">
+        <v>61.6162109375</v>
+      </c>
+      <c r="I81" t="n">
+        <v>2.399310343254057</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1.891530886041618</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-10-08 05:45:48</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>24</v>
+      </c>
+      <c r="F82" t="n">
+        <v>2571.441162109375</v>
       </c>
     </row>
   </sheetData>
@@ -3508,7 +3546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8424,6 +8462,24 @@
           <t>2618.074707,2617.949219,2618.990479,2620.362793,2621.037354,2622.362061,2622.535889,2621.193115,2621.126953,2622.045410,2621.487305,2622.362793,2623.988525,2623.908447,2625.387939,2626.036621,2627.977051,2628.131836,2629.533447,2628.958984,2629.551758,2630.001953,2629.766846,2629.696289</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2617.489990,2615.810059,2608.969971,2596.250000,2579.090088,2577.379883,2571.989990,2568.459961,2562.459961,2569.399902,2567.189941,2549.919922,2561.199951,2569.550049,2572.760010,2566.260010,2568.229980,2572.800049,2574.520020,2576.449951,2578.590088,2562.520020,2560.820068,2568.080078</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>0.584717,2.139160,10.020508,24.112793,41.947266,44.982178,50.545899,52.733154,58.666992,52.645508,54.297364,72.442871,62.788574,54.358398,52.627929,59.776611,59.747071,55.331787,55.013427,52.509033,50.961670,67.481933,68.946778,61.616211</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>0.022339,0.081778,0.384079,0.928755,1.626437,1.745268,1.965245,2.053104,2.289479,2.048942,2.115050,2.840986,2.451530,2.115483,2.045583,2.329328,2.326391,2.150645,2.136842,2.038038,1.976339,2.633421,2.692371,2.399310</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>1.891530886041618</v>
+      </c>
       <c r="K81" t="inlineStr">
         <is>
           <t>2617.733154,2620.394043,2619.939697,2623.072510,2623.275146,2623.920898,2624.219971,2622.112793,2622.322754,2622.193848,2622.860352,2624.614258,2623.211670,2624.654785,2625.150391,2622.911133,2626.169189,2627.363037,2627.479004,2626.092041,2627.390381,2623.437256,2625.868652,2625.049072</t>
@@ -8437,6 +8493,49 @@
       <c r="M81" t="inlineStr">
         <is>
           <t>2607.321045,2603.148193,2600.191650,2599.215332,2597.103516,2595.414551,2593.614014,2591.076660,2589.803223,2588.280273,2584.581543,2585.843018,2586.658691,2585.708984,2586.866943,2586.392090,2587.471191,2586.526855,2586.495117,2585.808838,2585.367920,2584.298584,2583.410889,2583.857178</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-10-08 05:45:48</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>24</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2566.703613,2567.367676,2567.937988,2568.096924,2568.709961,2569.568359,2569.959717,2569.446045,2569.042236,2569.951904,2569.697021,2570.634033,2571.317383,2572.153809,2572.724854,2572.440430,2572.142578,2572.871094,2573.676025,2573.566406,2573.719727,2572.425293,2571.509521,2571.441162</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>2568.388916,2569.071045,2567.351562,2569.833984,2569.754639,2573.449707,2573.352295,2568.697266,2574.179443,2572.824463,2575.111816,2575.632324,2576.610840,2576.534180,2578.278076,2574.988281,2576.232178,2580.095215,2579.772461,2575.334961,2577.509521,2575.094971,2577.679688,2573.609131</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2557.253418,2554.965088,2551.082764,2548.915771,2546.443604,2543.684082,2545.782471,2543.048096,2538.090088,2536.363525,2532.975586,2535.301758,2532.516113,2532.680664,2531.156250,2528.465820,2526.814941,2525.703857,2521.796631,2520.418457,2518.393799,2516.602539,2514.657715,2513.354980</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2562.139648,2559.710205,2556.946777,2554.993408,2553.074951,2553.535156,2552.528809,2551.025146,2551.048096,2548.863037,2545.733398,2547.219727,2547.220703,2547.184570,2548.373535,2546.277588,2544.138672,2541.836426,2543.096191,2543.411865,2541.898926,2537.381592,2536.452881,2536.428955</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3533,6 +3533,44 @@
       </c>
       <c r="F82" t="n">
         <v>2571.441162109375</v>
+      </c>
+      <c r="G82" t="n">
+        <v>2488.580078125</v>
+      </c>
+      <c r="H82" t="n">
+        <v>82.861083984375</v>
+      </c>
+      <c r="I82" t="n">
+        <v>3.32965311073317</v>
+      </c>
+      <c r="J82" t="n">
+        <v>3.037614977610442</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-10-09 05:49:51</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>24</v>
+      </c>
+      <c r="F83" t="n">
+        <v>2494.312255859375</v>
       </c>
     </row>
   </sheetData>
@@ -3546,7 +3584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8523,6 +8561,24 @@
           <t>2566.703613,2567.367676,2567.937988,2568.096924,2568.709961,2569.568359,2569.959717,2569.446045,2569.042236,2569.951904,2569.697021,2570.634033,2571.317383,2572.153809,2572.724854,2572.440430,2572.142578,2572.871094,2573.676025,2573.566406,2573.719727,2572.425293,2571.509521,2571.441162</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2564.959961,2566.560059,2558.090088,2565.919922,2549.300049,2535.379883,2527.860107,2520.340088,2529.979980,2433.350098,2414.550049,2415.790039,2445.810059,2462.840088,2473.770020,2477.229980,2474.389893,2472.889893,2476.370117,2480.530029,2487.459961,2491.310059,2485.120117,2488.580078</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>1.743652,0.807617,9.847900,2.177002,19.409912,34.188476,42.099610,49.105957,39.062256,136.601806,155.146972,154.843994,125.507324,109.313721,98.954834,95.210450,97.752685,99.981201,97.305908,93.036377,86.259766,81.115234,86.389404,82.861084</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>0.067980,0.031467,0.384971,0.084843,0.761382,1.348456,1.665425,1.948386,1.543975,5.613734,6.425502,6.409663,5.131524,4.438523,4.000163,3.843424,3.950577,4.043092,3.929377,3.750665,3.467785,3.255927,3.476267,3.329653</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>3.037614977610442</v>
+      </c>
       <c r="K82" t="inlineStr">
         <is>
           <t>2568.388916,2569.071045,2567.351562,2569.833984,2569.754639,2573.449707,2573.352295,2568.697266,2574.179443,2572.824463,2575.111816,2575.632324,2576.610840,2576.534180,2578.278076,2574.988281,2576.232178,2580.095215,2579.772461,2575.334961,2577.509521,2575.094971,2577.679688,2573.609131</t>
@@ -8536,6 +8592,49 @@
       <c r="M82" t="inlineStr">
         <is>
           <t>2562.139648,2559.710205,2556.946777,2554.993408,2553.074951,2553.535156,2552.528809,2551.025146,2551.048096,2548.863037,2545.733398,2547.219727,2547.220703,2547.184570,2548.373535,2546.277588,2544.138672,2541.836426,2543.096191,2543.411865,2541.898926,2537.381592,2536.452881,2536.428955</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-10-09 05:49:51</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>24</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2489.338623,2489.878662,2490.147217,2489.605469,2489.519043,2489.963135,2490.115967,2489.603027,2488.762695,2488.735352,2486.795410,2488.227783,2488.268311,2489.928467,2490.149902,2490.563477,2490.529297,2492.790283,2493.462402,2494.053955,2494.153564,2495.008301,2494.064697,2494.312256</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>2492.709961,2492.307861,2488.060547,2491.729980,2491.483398,2493.405518,2495.176025,2488.980469,2493.691162,2492.402588,2490.668945,2492.407471,2497.180176,2495.992920,2496.415527,2496.054199,2499.297119,2501.773438,2501.869629,2498.197510,2500.197510,2500.765625,2503.247070,2500.735352</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2470.748047,2467.095215,2462.731689,2459.802734,2455.623047,2453.390869,2453.854492,2451.735840,2446.321533,2443.172119,2437.578125,2440.092773,2436.121338,2435.999756,2434.406494,2433.157227,2432.192139,2432.443604,2427.623291,2425.945068,2424.173828,2426.202393,2424.445801,2423.473633</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2479.189453,2476.222900,2474.209229,2470.476807,2468.821045,2467.825439,2466.500000,2464.695068,2464.353271,2461.966309,2455.598877,2457.812744,2455.370361,2455.892822,2457.032227,2456.154297,2453.777344,2454.120605,2454.065918,2454.602783,2452.182129,2450.546143,2450.796143,2451.611328</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3571,6 +3571,44 @@
       </c>
       <c r="F83" t="n">
         <v>2494.312255859375</v>
+      </c>
+      <c r="G83" t="n">
+        <v>2495.1201171875</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.807861328125</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.03237765278553489</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.2484437346223259</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-10-10 05:33:13</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>24</v>
+      </c>
+      <c r="F84" t="n">
+        <v>2492.476806640625</v>
       </c>
     </row>
   </sheetData>
@@ -3584,7 +3622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8622,6 +8660,24 @@
           <t>2489.338623,2489.878662,2490.147217,2489.605469,2489.519043,2489.963135,2490.115967,2489.603027,2488.762695,2488.735352,2486.795410,2488.227783,2488.268311,2489.928467,2490.149902,2490.563477,2490.529297,2492.790283,2493.462402,2494.053955,2494.153564,2495.008301,2494.064697,2494.312256</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2497.389893,2502.540039,2503.169922,2500.110107,2490.560059,2504.219971,2495.800049,2482.699951,2488.810059,2487.000000,2489.439941,2485.699951,2481.129883,2474.379883,2480.719971,2482.879883,2486.889893,2485.229980,2487.100098,2493.360107,2490.860107,2489.139893,2492.639893,2495.120117</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>8.051270,12.661377,13.022705,10.504638,1.041016,14.256836,5.684082,6.903076,0.047364,1.735352,2.644531,2.527832,7.138428,15.548584,9.429931,7.683594,3.639404,7.560303,6.362304,0.693848,3.293457,5.868408,1.424804,0.807861</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>0.322387,0.505941,0.520249,0.420167,0.041798,0.569312,0.227746,0.278047,0.001903,0.069777,0.106230,0.101695,0.287709,0.628383,0.380129,0.309463,0.146344,0.304209,0.255812,0.027828,0.132222,0.235760,0.057160,0.032378</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>0.2484437346223259</v>
+      </c>
       <c r="K83" t="inlineStr">
         <is>
           <t>2492.709961,2492.307861,2488.060547,2491.729980,2491.483398,2493.405518,2495.176025,2488.980469,2493.691162,2492.402588,2490.668945,2492.407471,2497.180176,2495.992920,2496.415527,2496.054199,2499.297119,2501.773438,2501.869629,2498.197510,2500.197510,2500.765625,2503.247070,2500.735352</t>
@@ -8635,6 +8691,49 @@
       <c r="M83" t="inlineStr">
         <is>
           <t>2479.189453,2476.222900,2474.209229,2470.476807,2468.821045,2467.825439,2466.500000,2464.695068,2464.353271,2461.966309,2455.598877,2457.812744,2455.370361,2455.892822,2457.032227,2456.154297,2453.777344,2454.120605,2454.065918,2454.602783,2452.182129,2450.546143,2450.796143,2451.611328</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-10-10 05:33:13</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>24</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2496.246094,2496.480469,2497.001953,2495.281738,2495.716797,2494.950928,2494.850342,2493.673828,2493.012695,2492.958252,2491.802246,2492.317627,2492.177490,2492.546875,2492.597168,2491.920410,2490.977295,2492.705811,2491.813477,2493.160400,2491.711182,2492.192383,2491.566162,2492.476807</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>2498.591064,2498.223633,2494.008057,2494.238281,2494.562012,2497.100098,2494.494629,2490.968750,2495.640137,2494.631836,2491.221924,2492.400391,2495.745117,2493.544189,2495.899902,2492.708496,2493.928955,2494.763184,2495.510010,2493.670410,2493.069824,2493.752197,2493.932373,2492.739746</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2482.142334,2479.365723,2475.949219,2472.784180,2470.723633,2468.189453,2468.195068,2464.962891,2460.526611,2458.406982,2454.177002,2455.437012,2451.127686,2450.806152,2450.095215,2447.044678,2445.953613,2445.363281,2440.927734,2442.149170,2438.723633,2439.934814,2438.750488,2437.183838</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2488.781494,2485.982666,2483.587891,2480.615234,2479.429932,2478.717529,2477.384033,2474.393799,2474.345703,2472.089600,2468.110352,2468.534912,2466.697021,2466.772949,2467.293701,2464.983887,2462.868164,2462.321777,2461.612061,2463.684570,2460.821777,2459.769287,2459.545654,2460.155029</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3609,6 +3609,44 @@
       </c>
       <c r="F84" t="n">
         <v>2492.476806640625</v>
+      </c>
+      <c r="G84" t="n">
+        <v>2506.090087890625</v>
+      </c>
+      <c r="H84" t="n">
+        <v>13.61328125</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.5432079762726444</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.3971254204479794</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-10-11 05:28:24</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>24</v>
+      </c>
+      <c r="F85" t="n">
+        <v>2508.078125</v>
       </c>
     </row>
   </sheetData>
@@ -3622,7 +3660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8721,6 +8759,24 @@
           <t>2496.246094,2496.480469,2497.001953,2495.281738,2495.716797,2494.950928,2494.850342,2493.673828,2493.012695,2492.958252,2491.802246,2492.317627,2492.177490,2492.546875,2492.597168,2491.920410,2490.977295,2492.705811,2491.813477,2493.160400,2491.711182,2492.192383,2491.566162,2492.476807</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2491.139893,2492.919922,2493.659912,2494.550049,2493.669922,2494.899902,2494.129883,2497.149902,2506.010010,2509.419922,2503.050049,2505.719971,2509.580078,2510.860107,2506.010010,2507.580078,2507.669922,2503.860107,2501.739990,2508.179932,2508.260010,2497.000000,2504.689941,2506.090088</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>5.106201,3.560547,3.342041,0.731689,2.046875,0.051026,0.720459,3.476074,12.997315,16.461670,11.247803,13.402344,17.402588,18.313232,13.412842,15.659668,16.692627,11.154296,9.926513,15.019532,16.548828,4.807617,13.123779,13.613281</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>0.204974,0.142826,0.134022,0.029332,0.082083,0.002045,0.028886,0.139202,0.518646,0.655995,0.449364,0.534870,0.693446,0.729361,0.535227,0.624493,0.665663,0.445484,0.396784,0.598822,0.659773,0.192536,0.523968,0.543208</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>0.3971254204479794</v>
+      </c>
       <c r="K84" t="inlineStr">
         <is>
           <t>2498.591064,2498.223633,2494.008057,2494.238281,2494.562012,2497.100098,2494.494629,2490.968750,2495.640137,2494.631836,2491.221924,2492.400391,2495.745117,2493.544189,2495.899902,2492.708496,2493.928955,2494.763184,2495.510010,2493.670410,2493.069824,2493.752197,2493.932373,2492.739746</t>
@@ -8734,6 +8790,49 @@
       <c r="M84" t="inlineStr">
         <is>
           <t>2488.781494,2485.982666,2483.587891,2480.615234,2479.429932,2478.717529,2477.384033,2474.393799,2474.345703,2472.089600,2468.110352,2468.534912,2466.697021,2466.772949,2467.293701,2464.983887,2462.868164,2462.321777,2461.612061,2463.684570,2460.821777,2459.769287,2459.545654,2460.155029</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-10-11 05:28:24</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>24</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2506.265625,2506.960449,2507.444336,2506.565674,2507.917480,2507.650146,2508.049805,2507.221924,2506.935303,2507.110596,2507.718018,2506.560791,2507.498779,2507.642334,2507.645752,2506.339355,2506.859131,2507.585449,2507.503418,2507.350342,2507.119385,2508.405273,2507.647949,2508.078125</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>2507.305420,2507.743164,2505.341797,2506.130127,2506.582275,2507.950195,2507.587402,2504.580811,2508.849854,2507.920654,2507.965332,2506.275391,2508.622803,2506.289062,2509.422852,2505.223877,2509.384521,2509.466064,2509.632812,2507.667969,2508.860107,2509.308838,2508.462891,2507.726807</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2496.221924,2494.796631,2492.702637,2491.041016,2489.918213,2489.120361,2489.169922,2486.512939,2483.447266,2483.041992,2480.809326,2479.946289,2477.843750,2478.130859,2476.681885,2473.500000,2473.090088,2472.849121,2469.846191,2469.287354,2468.003418,2469.056152,2468.322266,2466.810059</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2501.365967,2499.553955,2498.019531,2496.769043,2497.108643,2496.534180,2496.099365,2494.144043,2494.784668,2493.230469,2492.401611,2490.771240,2490.631104,2490.101562,2490.637939,2487.532471,2487.402100,2486.960449,2486.902344,2487.136719,2485.935303,2486.048340,2484.864014,2485.182129</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3647,6 +3647,44 @@
       </c>
       <c r="F85" t="n">
         <v>2508.078125</v>
+      </c>
+      <c r="G85" t="n">
+        <v>2555.47998046875</v>
+      </c>
+      <c r="H85" t="n">
+        <v>47.40185546875</v>
+      </c>
+      <c r="I85" t="n">
+        <v>1.854910068990449</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.8922575163766587</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-10-12 05:39:32</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>24</v>
+      </c>
+      <c r="F86" t="n">
+        <v>2560.880615234375</v>
       </c>
     </row>
   </sheetData>
@@ -3660,7 +3698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8820,6 +8858,24 @@
           <t>2506.265625,2506.960449,2507.444336,2506.565674,2507.917480,2507.650146,2508.049805,2507.221924,2506.935303,2507.110596,2507.718018,2506.560791,2507.498779,2507.642334,2507.645752,2506.339355,2506.859131,2507.585449,2507.503418,2507.350342,2507.119385,2508.405273,2507.647949,2508.078125</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2503.610107,2498.409912,2498.459961,2500.199951,2498.330078,2503.639893,2502.489990,2500.080078,2505.419922,2532.989990,2547.949951,2536.070068,2532.520020,2533.909912,2535.149902,2527.030029,2530.719971,2534.219971,2543.399902,2539.179932,2544.729980,2543.050049,2563.870117,2555.479980</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2.655518,8.550537,8.984375,6.365723,9.587402,4.010253,5.559815,7.141846,1.515381,25.879394,40.231933,29.509277,25.021241,26.267578,27.504150,20.690674,23.860840,26.634522,35.896484,31.829590,37.610595,34.644776,56.222168,47.401855</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>0.106068,0.342239,0.359597,0.254609,0.383752,0.160177,0.222171,0.285665,0.060484,1.021694,1.578992,1.163583,0.987998,1.036642,1.084912,0.818774,0.942848,1.050995,1.411358,1.253538,1.477980,1.362332,2.192863,1.854910</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>0.8922575163766587</v>
+      </c>
       <c r="K85" t="inlineStr">
         <is>
           <t>2507.305420,2507.743164,2505.341797,2506.130127,2506.582275,2507.950195,2507.587402,2504.580811,2508.849854,2507.920654,2507.965332,2506.275391,2508.622803,2506.289062,2509.422852,2505.223877,2509.384521,2509.466064,2509.632812,2507.667969,2508.860107,2509.308838,2508.462891,2507.726807</t>
@@ -8833,6 +8889,49 @@
       <c r="M85" t="inlineStr">
         <is>
           <t>2501.365967,2499.553955,2498.019531,2496.769043,2497.108643,2496.534180,2496.099365,2494.144043,2494.784668,2493.230469,2492.401611,2490.771240,2490.631104,2490.101562,2490.637939,2487.532471,2487.402100,2486.960449,2486.902344,2487.136719,2485.935303,2486.048340,2484.864014,2485.182129</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-10-12 05:39:32</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>24</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2553.979492,2554.421387,2554.457275,2554.661621,2555.916016,2556.418945,2556.818604,2557.137207,2557.489746,2557.713623,2558.500977,2558.218994,2559.205811,2559.310303,2559.386963,2559.313232,2559.969482,2560.080078,2559.554688,2560.254150,2559.565430,2560.508545,2560.553223,2560.880615</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>2555.057861,2554.976318,2554.502930,2553.124023,2554.229736,2555.697510,2555.660645,2556.006836,2557.053711,2556.568604,2559.371094,2556.108887,2559.003174,2558.683105,2559.282715,2559.761719,2559.743652,2559.499756,2559.348389,2560.165527,2559.965332,2561.202881,2560.937988,2559.735107</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2536.922607,2534.500977,2532.047363,2530.690186,2529.085205,2528.317871,2527.712402,2527.367676,2525.432129,2524.945801,2522.832520,2522.801270,2521.784912,2521.790039,2519.948486,2517.703613,2517.485840,2516.571533,2511.502930,2511.674805,2510.370361,2511.604980,2511.177490,2510.303955</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2544.991211,2542.137207,2539.911621,2539.937500,2539.012695,2538.436279,2537.773682,2538.028320,2538.168213,2537.818359,2537.043701,2536.466797,2536.639160,2536.571289,2535.825684,2533.887939,2534.624023,2533.281494,2531.220459,2531.911377,2530.439209,2530.453125,2530.450439,2531.531494</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3685,6 +3685,44 @@
       </c>
       <c r="F86" t="n">
         <v>2560.880615234375</v>
+      </c>
+      <c r="G86" t="n">
+        <v>2528.659912109375</v>
+      </c>
+      <c r="H86" t="n">
+        <v>32.220703125</v>
+      </c>
+      <c r="I86" t="n">
+        <v>1.274220505916982</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1.862768951366293</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:35:47</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>24</v>
+      </c>
+      <c r="F87" t="n">
+        <v>2536.842041015625</v>
       </c>
     </row>
   </sheetData>
@@ -3698,7 +3736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8919,6 +8957,24 @@
           <t>2553.979492,2554.421387,2554.457275,2554.661621,2555.916016,2556.418945,2556.818604,2557.137207,2557.489746,2557.713623,2558.500977,2558.218994,2559.205811,2559.310303,2559.386963,2559.313232,2559.969482,2560.080078,2559.554688,2560.254150,2559.565430,2560.508545,2560.553223,2560.880615</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2568.100098,2561.570068,2549.479980,2557.699951,2553.350098,2543.570068,2529.350098,2539.560059,2521.020020,2527.610107,2510.860107,2508.969971,2510.770020,2518.459961,2516.110107,2487.709961,2465.729980,2444.300049,2418.520020,2461.540039,2488.820068,2505.620117,2514.669922,2528.659912</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>14.120606,7.148681,4.977295,3.038330,2.565918,12.848877,27.468506,17.577148,36.469726,30.103516,47.640870,49.249023,48.435791,40.850342,43.276856,71.603271,94.239502,115.780029,141.034668,98.714111,70.745362,54.888428,45.883301,32.220703</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>0.549846,0.279074,0.195228,0.118792,0.100492,0.505151,1.085991,0.692134,1.446626,1.190987,1.897392,1.962918,1.929121,1.622037,1.719991,2.878281,3.821972,4.736736,5.831445,4.010258,2.842526,2.190613,1.824625,1.274220</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>1.862768951366293</v>
+      </c>
       <c r="K86" t="inlineStr">
         <is>
           <t>2555.057861,2554.976318,2554.502930,2553.124023,2554.229736,2555.697510,2555.660645,2556.006836,2557.053711,2556.568604,2559.371094,2556.108887,2559.003174,2558.683105,2559.282715,2559.761719,2559.743652,2559.499756,2559.348389,2560.165527,2559.965332,2561.202881,2560.937988,2559.735107</t>
@@ -8932,6 +8988,49 @@
       <c r="M86" t="inlineStr">
         <is>
           <t>2544.991211,2542.137207,2539.911621,2539.937500,2539.012695,2538.436279,2537.773682,2538.028320,2538.168213,2537.818359,2537.043701,2536.466797,2536.639160,2536.571289,2535.825684,2533.887939,2534.624023,2533.281494,2531.220459,2531.911377,2530.439209,2530.453125,2530.450439,2531.531494</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:35:47</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>24</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2533.344971,2534.322266,2533.770020,2533.168213,2533.386963,2533.159668,2533.215820,2532.992920,2533.242920,2533.679443,2534.001221,2533.787354,2534.646973,2534.100586,2533.958984,2533.382568,2534.316406,2534.182861,2534.110596,2534.316406,2533.789551,2534.865723,2536.283447,2536.842041</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>2534.448975,2533.580322,2533.599609,2532.166504,2530.140625,2532.367432,2533.336914,2531.513184,2532.377686,2531.897949,2532.872803,2532.657227,2534.161865,2533.297852,2533.855469,2530.668701,2533.558594,2533.915771,2532.264893,2533.736572,2534.121094,2533.978027,2536.451172,2537.054688</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2512.123779,2507.687256,2502.739746,2499.370117,2495.632568,2493.150635,2491.246582,2488.399658,2486.241455,2484.773193,2482.416992,2482.000488,2481.494141,2479.136719,2477.739746,2475.857422,2476.177979,2474.717041,2470.427246,2470.427979,2468.680176,2470.120850,2471.001953,2469.813477</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2521.572510,2518.321533,2514.350098,2512.620850,2510.150146,2508.378418,2506.439941,2504.912109,2504.509033,2504.270020,2502.496826,2502.196289,2501.660400,2500.618652,2500.383057,2498.587891,2498.744629,2497.524902,2496.322510,2496.914795,2495.519531,2495.313965,2496.668457,2498.031982</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3723,6 +3723,44 @@
       </c>
       <c r="F87" t="n">
         <v>2536.842041015625</v>
+      </c>
+      <c r="G87" t="n">
+        <v>2514.510009765625</v>
+      </c>
+      <c r="H87" t="n">
+        <v>22.33203125</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.8881265599766511</v>
+      </c>
+      <c r="J87" t="n">
+        <v>1.032055537161822</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-10-14 04:36:26</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>24</v>
+      </c>
+      <c r="F88" t="n">
+        <v>2517.049560546875</v>
       </c>
     </row>
   </sheetData>
@@ -3736,7 +3774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9018,6 +9056,24 @@
           <t>2533.344971,2534.322266,2533.770020,2533.168213,2533.386963,2533.159668,2533.215820,2532.992920,2533.242920,2533.679443,2534.001221,2533.787354,2534.646973,2534.100586,2533.958984,2533.382568,2534.316406,2534.182861,2534.110596,2534.316406,2533.789551,2534.865723,2536.283447,2536.842041</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2526.689941,2515.209961,2511.600098,2495.929932,2497.229980,2502.090088,2500.520020,2514.030029,2513.699951,2510.229980,2498.310059,2506.370117,2505.310059,2508.310059,2510.090088,2509.010010,2495.639893,2505.370117,2503.879883,2511.919922,2511.139893,2514.510010,2514.510010,2514.510010</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>6.655030,19.112305,22.169922,37.238281,36.156983,31.069580,32.695800,18.962891,19.542969,23.449463,35.691162,27.417237,29.336914,25.790527,23.868896,24.372558,38.676513,28.812744,30.230713,22.396484,22.649658,20.355713,21.773437,22.332031</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>0.263389,0.759869,0.882701,1.491960,1.447884,1.241745,1.307560,0.754283,0.777458,0.934156,1.428612,1.093902,1.170989,1.028203,0.950918,0.971401,1.549763,1.150039,1.207355,0.891608,0.901967,0.809530,0.865912,0.888127</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>1.032055537161822</v>
+      </c>
       <c r="K87" t="inlineStr">
         <is>
           <t>2534.448975,2533.580322,2533.599609,2532.166504,2530.140625,2532.367432,2533.336914,2531.513184,2532.377686,2531.897949,2532.872803,2532.657227,2534.161865,2533.297852,2533.855469,2530.668701,2533.558594,2533.915771,2532.264893,2533.736572,2534.121094,2533.978027,2536.451172,2537.054688</t>
@@ -9031,6 +9087,49 @@
       <c r="M87" t="inlineStr">
         <is>
           <t>2521.572510,2518.321533,2514.350098,2512.620850,2510.150146,2508.378418,2506.439941,2504.912109,2504.509033,2504.270020,2502.496826,2502.196289,2501.660400,2500.618652,2500.383057,2498.587891,2498.744629,2497.524902,2496.322510,2496.914795,2495.519531,2495.313965,2496.668457,2498.031982</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-10-14 04:36:26</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>24</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2514.819580,2515.246582,2515.331299,2515.456787,2515.930664,2515.321289,2514.733398,2514.583008,2515.048828,2514.528564,2515.032959,2515.452881,2516.111572,2516.158447,2515.971924,2515.998779,2516.470215,2516.649658,2516.181641,2516.239014,2516.323242,2516.362061,2516.920654,2517.049561</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>2515.536621,2514.775391,2514.610596,2514.752686,2513.831055,2514.478027,2514.205322,2514.674561,2514.888184,2514.387207,2514.336182,2514.956543,2516.748291,2516.303467,2517.838135,2514.938965,2518.015869,2517.306641,2517.143066,2517.178711,2518.066895,2517.215576,2517.996338,2517.927734</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2500.821777,2497.625488,2494.337891,2493.103027,2490.447266,2488.619141,2486.340088,2484.607910,2482.446289,2480.256348,2478.507812,2479.659180,2477.614746,2477.209961,2475.016357,2473.548828,2473.321777,2472.481934,2467.857910,2467.901123,2467.617432,2467.653564,2467.220215,2465.278564</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2507.094238,2504.697266,2502.174316,2501.669678,2500.529785,2498.743896,2497.012451,2495.981689,2496.585449,2494.462158,2493.528564,2493.950684,2493.362549,2492.565186,2492.039307,2491.114258,2491.021484,2489.463867,2488.821533,2489.176270,2488.687012,2487.085938,2487.557129,2487.477539</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3761,6 +3761,44 @@
       </c>
       <c r="F88" t="n">
         <v>2517.049560546875</v>
+      </c>
+      <c r="G88" t="n">
+        <v>2364.8701171875</v>
+      </c>
+      <c r="H88" t="n">
+        <v>152.179443359375</v>
+      </c>
+      <c r="I88" t="n">
+        <v>6.435002170028663</v>
+      </c>
+      <c r="J88" t="n">
+        <v>3.030934686491263</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-10-15 04:19:01</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>24</v>
+      </c>
+      <c r="F89" t="n">
+        <v>2380.8271484375</v>
       </c>
     </row>
   </sheetData>
@@ -3774,7 +3812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:M89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9117,6 +9155,24 @@
           <t>2514.819580,2515.246582,2515.331299,2515.456787,2515.930664,2515.321289,2514.733398,2514.583008,2515.048828,2514.528564,2515.032959,2515.452881,2516.111572,2516.158447,2515.971924,2515.998779,2516.470215,2516.649658,2516.181641,2516.239014,2516.323242,2516.362061,2516.920654,2517.049561</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2500.879883,2502.389893,2508.600098,2503.649902,2494.550049,2504.719971,2502.020020,2473.989990,2450.489990,2431.560059,2427.149902,2445.959961,2428.770020,2428.889893,2427.929932,2414.040039,2417.199951,2415.679932,2418.550049,2415.929932,2410.239990,2377.000000,2357.110107,2364.870117</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>13.939697,12.856689,6.731201,11.806885,21.380615,10.601318,12.713378,40.593018,64.558838,82.968505,87.883057,69.492920,87.341552,87.268554,88.041992,101.958740,99.270264,100.969726,97.631592,100.309082,106.083252,139.362061,159.810547,152.179444</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>0.557392,0.513776,0.268325,0.471587,0.857093,0.423254,0.508125,1.640792,2.634528,3.412151,3.620833,2.841131,3.596123,3.592940,3.626216,4.223573,4.106829,4.179764,4.036782,4.151986,4.401356,5.862939,6.779936,6.435002</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>3.030934686491263</v>
+      </c>
       <c r="K88" t="inlineStr">
         <is>
           <t>2515.536621,2514.775391,2514.610596,2514.752686,2513.831055,2514.478027,2514.205322,2514.674561,2514.888184,2514.387207,2514.336182,2514.956543,2516.748291,2516.303467,2517.838135,2514.938965,2518.015869,2517.306641,2517.143066,2517.178711,2518.066895,2517.215576,2517.996338,2517.927734</t>
@@ -9130,6 +9186,49 @@
       <c r="M88" t="inlineStr">
         <is>
           <t>2507.094238,2504.697266,2502.174316,2501.669678,2500.529785,2498.743896,2497.012451,2495.981689,2496.585449,2494.462158,2493.528564,2493.950684,2493.362549,2492.565186,2492.039307,2491.114258,2491.021484,2489.463867,2488.821533,2489.176270,2488.687012,2487.085938,2487.557129,2487.477539</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-10-15 04:19:01</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>24</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2370.122803,2369.894043,2369.915283,2369.844727,2370.297119,2370.062012,2370.935303,2370.533691,2370.426758,2370.354004,2370.453857,2371.702637,2372.928467,2374.861816,2374.715088,2375.155029,2374.909424,2377.190186,2377.083496,2378.588135,2378.378906,2379.601562,2379.940674,2380.827148</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>2373.606445,2371.809326,2369.903320,2372.841797,2373.016357,2373.327148,2375.302246,2372.806152,2376.058838,2377.622314,2373.125244,2378.504395,2379.693359,2379.769775,2381.768311,2380.233154,2381.578857,2385.782471,2382.758789,2385.780762,2387.480957,2381.987793,2389.225586,2390.478516</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2345.999512,2340.268311,2335.640381,2332.621826,2329.736084,2327.875488,2327.466309,2323.848877,2321.983398,2319.270264,2317.596680,2319.437988,2317.708008,2317.434814,2316.950928,2316.302002,2315.402832,2316.450928,2312.075928,2313.440186,2311.643555,2311.877930,2312.797363,2310.389160</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2356.112549,2351.918213,2349.261230,2346.829834,2345.780762,2345.013916,2344.102539,2341.688232,2342.592285,2340.521973,2338.390625,2341.110596,2339.265137,2339.692139,2341.058350,2339.854004,2338.310059,2339.317139,2339.756348,2341.557861,2339.041748,2339.128418,2339.138672,2340.272949</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3799,6 +3799,44 @@
       </c>
       <c r="F89" t="n">
         <v>2380.8271484375</v>
+      </c>
+      <c r="G89" t="n">
+        <v>2437.280029296875</v>
+      </c>
+      <c r="H89" t="n">
+        <v>56.452880859375</v>
+      </c>
+      <c r="I89" t="n">
+        <v>2.316224651283134</v>
+      </c>
+      <c r="J89" t="n">
+        <v>1.838993849911677</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:14:34</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>24</v>
+      </c>
+      <c r="F90" t="n">
+        <v>2443.7138671875</v>
       </c>
     </row>
   </sheetData>
@@ -3812,7 +3850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M89"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9216,6 +9254,24 @@
           <t>2370.122803,2369.894043,2369.915283,2369.844727,2370.297119,2370.062012,2370.935303,2370.533691,2370.426758,2370.354004,2370.453857,2371.702637,2372.928467,2374.861816,2374.715088,2375.155029,2374.909424,2377.190186,2377.083496,2378.588135,2378.378906,2379.601562,2379.940674,2380.827148</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2346.520020,2355.159912,2376.860107,2371.070068,2372.500000,2365.070068,2360.139893,2347.070068,2337.739990,2394.590088,2438.139893,2431.959961,2443.820068,2448.909912,2450.570068,2451.510010,2459.159912,2453.129883,2438.689941,2438.340088,2430.149902,2436.169922,2436.810059,2437.280029</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>23.602783,14.734131,6.944824,1.225341,2.202881,4.991944,10.795410,23.463623,32.686768,24.236084,67.686036,60.257324,70.891601,74.048096,75.854980,76.354981,84.250488,75.939697,61.606445,59.751953,51.770996,56.568360,56.869385,56.452881</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1.005863,0.625611,0.292185,0.051679,0.092851,0.211070,0.457406,0.999698,1.398221,1.012118,2.776134,2.477727,2.900852,3.023717,3.095401,3.114610,3.425987,3.095625,2.526211,2.450518,2.130362,2.322020,2.333764,2.316225</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>1.838993849911677</v>
+      </c>
       <c r="K89" t="inlineStr">
         <is>
           <t>2373.606445,2371.809326,2369.903320,2372.841797,2373.016357,2373.327148,2375.302246,2372.806152,2376.058838,2377.622314,2373.125244,2378.504395,2379.693359,2379.769775,2381.768311,2380.233154,2381.578857,2385.782471,2382.758789,2385.780762,2387.480957,2381.987793,2389.225586,2390.478516</t>
@@ -9229,6 +9285,49 @@
       <c r="M89" t="inlineStr">
         <is>
           <t>2356.112549,2351.918213,2349.261230,2346.829834,2345.780762,2345.013916,2344.102539,2341.688232,2342.592285,2340.521973,2338.390625,2341.110596,2339.265137,2339.692139,2341.058350,2339.854004,2338.310059,2339.317139,2339.756348,2341.557861,2339.041748,2339.128418,2339.138672,2340.272949</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-10-16 04:14:34</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>24</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2437.725830,2438.104004,2439.001221,2438.985107,2440.024414,2438.989502,2439.589355,2440.675781,2440.547607,2440.727539,2441.513428,2442.200439,2443.082520,2443.668945,2443.766846,2443.976807,2444.081055,2444.849854,2445.218994,2444.134033,2444.075195,2444.154541,2443.832520,2443.713867</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>2439.776611,2437.332031,2438.415039,2441.066895,2439.168945,2439.113770,2439.990967,2441.592041,2442.579102,2443.068115,2442.835205,2444.820068,2445.758789,2444.554199,2445.748291,2445.391357,2446.052734,2446.940918,2445.900635,2444.688232,2446.614014,2444.905029,2446.818359,2446.165771</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2416.837402,2412.575439,2408.809326,2406.820801,2404.286865,2401.296387,2399.378174,2398.272217,2394.800049,2392.504883,2391.572754,2391.381104,2388.762939,2388.813721,2386.990967,2386.205078,2384.619629,2384.026855,2379.744629,2378.143066,2377.615723,2376.580078,2374.966553,2371.903320</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2426.234619,2422.494385,2420.781006,2419.219727,2419.122559,2416.427734,2416.059814,2414.953857,2415.547852,2413.704590,2411.918213,2412.521484,2410.675781,2410.990234,2411.426514,2410.840088,2407.574463,2406.902588,2406.936279,2406.147461,2405.204590,2402.400635,2402.536865,2402.267090</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_60d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3837,6 +3837,44 @@
       </c>
       <c r="F90" t="n">
         <v>2443.7138671875</v>
+      </c>
+      <c r="G90" t="n">
+        <v>2423.320068359375</v>
+      </c>
+      <c r="H90" t="n">
+        <v>20.393798828125</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.841564393181125</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.8975101381700082</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-10-17 04:04:42</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>24</v>
+      </c>
+      <c r="F91" t="n">
+        <v>2428.7626953125</v>
       </c>
     </row>
   </sheetData>
@@ -3850,7 +3888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9315,6 +9353,24 @@
           <t>2437.725830,2438.104004,2439.001221,2438.985107,2440.024414,2438.989502,2439.589355,2440.675781,2440.547607,2440.727539,2441.513428,2442.200439,2443.082520,2443.668945,2443.766846,2443.976807,2444.081055,2444.849854,2445.218994,2444.134033,2444.075195,2444.154541,2443.832520,2443.713867</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2444.409912,2446.290039,2451.729980,2454.560059,2447.399902,2462.360107,2474.209961,2459.600098,2455.939941,2456.540039,2428.320068,2428.370117,2408.020020,2402.959961,2409.850098,2412.860107,2412.770020,2422.060059,2419.919922,2419.689941,2416.570068,2418.800049,2424.280029,2423.320068</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>6.684082,8.186035,12.728759,15.574952,7.375488,23.370605,34.620606,18.924317,15.392334,15.812500,13.193360,13.830322,35.062500,40.708984,33.916748,31.116700,31.311035,22.789795,25.299072,24.444092,27.505127,25.354492,19.552491,20.393799</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>0.273444,0.334631,0.519175,0.634531,0.301360,0.949114,1.399259,0.769406,0.626739,0.643690,0.543312,0.569531,1.456072,1.694118,1.407421,1.289619,1.297722,0.940926,1.045451,1.010216,1.138189,1.048226,0.806528,0.841564</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>0.8975101381700082</v>
+      </c>
       <c r="K90" t="inlineStr">
         <is>
           <t>2439.776611,2437.332031,2438.415039,2441.066895,2439.168945,2439.113770,2439.990967,2441.592041,2442.579102,2443.068115,2442.835205,2444.820068,2445.758789,2444.554199,2445.748291,2445.391357,2446.052734,2446.940918,2445.900635,2444.688232,2446.614014,2444.905029,2446.818359,2446.165771</t>
@@ -9328,6 +9384,49 @@
       <c r="M90" t="inlineStr">
         <is>
           <t>2426.234619,2422.494385,2420.781006,2419.219727,2419.122559,2416.427734,2416.059814,2414.953857,2415.547852,2413.704590,2411.918213,2412.521484,2410.675781,2410.990234,2411.426514,2410.840088,2407.574463,2406.902588,2406.936279,2406.147461,2405.204590,2402.400635,2402.536865,2402.267090</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-10-17 04:04:42</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>24</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2422.945557,2423.558350,2424.468018,2424.135986,2425.077148,2424.970703,2424.717529,2425.387207,2425.692139,2425.749268,2425.568848,2425.540039,2425.104248,2425.589355,2425.658691,2425.386230,2425.026367,2426.424561,2426.678711,2426.707031,2427.563232,2427.245605,2428.136719,2428.762695</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>2423.724609,2423.535400,2424.244385,2426.072510,2425.883545,2425.660156,2426.950684,2426.909180,2427.655029,2428.332031,2427.687256,2428.418701,2429.504639,2428.480713,2427.757324,2430.455566,2429.032227,2429.388184,2428.530518,2431.248779,2431.382080,2431.000244,2432.081055,2432.439941</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2406.114258,2403.546875,2401.868408,2400.240967,2398.662354,2397.250732,2395.281738,2394.166504,2391.695312,2389.135010,2386.680908,2386.561035,2384.145752,2384.584961,2381.835693,2381.136719,2378.003662,2379.090576,2374.809814,2373.798340,2373.652344,2373.101074,2372.258545,2370.669922</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2413.436523,2411.579102,2410.756836,2409.438965,2409.232910,2408.481201,2406.850586,2406.195068,2407.013916,2404.813721,2402.522461,2402.719727,2400.282471,2400.526855,2400.113525,2400.100342,2395.991455,2397.141846,2397.042480,2396.217041,2395.825684,2394.332275,2394.236084,2394.634766</t>
         </is>
       </c>
     </row>
